--- a/research/traditional_assets/database/data/china/china_food_wholesalers.xlsx
+++ b/research/traditional_assets/database/data/china/china_food_wholesalers.xlsx
@@ -1531,7 +1531,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1668,22 +1668,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07239088921648647</v>
+        <v>0.07224366199344524</v>
       </c>
       <c r="C2">
-        <v>45.05505344145492</v>
+        <v>44.70860887712093</v>
       </c>
       <c r="D2">
-        <v>20.75505344145491</v>
+        <v>20.87060887712093</v>
       </c>
       <c r="E2">
-        <v>-11.2</v>
+        <v>-10.738</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.462</v>
       </c>
       <c r="G2">
         <v>24.3</v>
@@ -1704,28 +1704,28 @@
         <v>5.36</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0232386</v>
       </c>
       <c r="N2">
-        <v>5.36</v>
+        <v>5.3367614</v>
       </c>
       <c r="O2">
-        <v>1.34</v>
+        <v>1.33419035</v>
       </c>
       <c r="P2">
-        <v>4.02</v>
+        <v>4.00257105</v>
       </c>
       <c r="Q2">
-        <v>4.06</v>
+        <v>4.04257105</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07239088921648647</v>
+        <v>0.07259233534691439</v>
       </c>
       <c r="T2">
-        <v>0.5044193424952811</v>
+        <v>0.5082407011505483</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1742,7 +1742,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>230.6507276686203</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1750,22 +1750,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07224366199344524</v>
+        <v>0.07209643477040403</v>
       </c>
       <c r="C3">
-        <v>44.70860887712093</v>
+        <v>44.36345824529521</v>
       </c>
       <c r="D3">
-        <v>20.87060887712093</v>
+        <v>20.98745824529521</v>
       </c>
       <c r="E3">
-        <v>-10.738</v>
+        <v>-10.276</v>
       </c>
       <c r="F3">
-        <v>0.462</v>
+        <v>0.924</v>
       </c>
       <c r="G3">
         <v>24.3</v>
@@ -1786,28 +1786,28 @@
         <v>5.36</v>
       </c>
       <c r="M3">
-        <v>0.0232386</v>
+        <v>0.0464772</v>
       </c>
       <c r="N3">
-        <v>5.3367614</v>
+        <v>5.3135228</v>
       </c>
       <c r="O3">
-        <v>1.33419035</v>
+        <v>1.3283807</v>
       </c>
       <c r="P3">
-        <v>4.00257105</v>
+        <v>3.9851421</v>
       </c>
       <c r="Q3">
-        <v>4.04257105</v>
+        <v>4.0251421</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07259233534691439</v>
+        <v>0.07279789262286125</v>
       </c>
       <c r="T3">
-        <v>0.5082407011505483</v>
+        <v>0.5121400467171476</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1824,7 +1824,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>230.6507276686203</v>
+        <v>115.3253638343102</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1832,22 +1832,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07209643477040403</v>
+        <v>0.07194920754736281</v>
       </c>
       <c r="C4">
-        <v>44.36345824529521</v>
+        <v>44.01962340156435</v>
       </c>
       <c r="D4">
-        <v>20.98745824529521</v>
+        <v>21.10562340156435</v>
       </c>
       <c r="E4">
-        <v>-10.276</v>
+        <v>-9.814</v>
       </c>
       <c r="F4">
-        <v>0.924</v>
+        <v>1.386</v>
       </c>
       <c r="G4">
         <v>24.3</v>
@@ -1868,28 +1868,28 @@
         <v>5.36</v>
       </c>
       <c r="M4">
-        <v>0.0464772</v>
+        <v>0.06971580000000001</v>
       </c>
       <c r="N4">
-        <v>5.3135228</v>
+        <v>5.2902842</v>
       </c>
       <c r="O4">
-        <v>1.3283807</v>
+        <v>1.32257105</v>
       </c>
       <c r="P4">
-        <v>3.9851421</v>
+        <v>3.96771315</v>
       </c>
       <c r="Q4">
-        <v>4.0251421</v>
+        <v>4.007713150000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07279789262286125</v>
+        <v>0.07300768819315753</v>
       </c>
       <c r="T4">
-        <v>0.5121400467171476</v>
+        <v>0.5161197911614087</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1906,7 +1906,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>115.3253638343102</v>
+        <v>76.8835758895401</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1914,22 +1914,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07194920754736281</v>
+        <v>0.0718019803243216</v>
       </c>
       <c r="C5">
-        <v>44.01962340156435</v>
+        <v>43.67712669651375</v>
       </c>
       <c r="D5">
-        <v>21.10562340156435</v>
+        <v>21.22512669651375</v>
       </c>
       <c r="E5">
-        <v>-9.814</v>
+        <v>-9.351999999999999</v>
       </c>
       <c r="F5">
-        <v>1.386</v>
+        <v>1.848</v>
       </c>
       <c r="G5">
         <v>24.3</v>
@@ -1950,28 +1950,28 @@
         <v>5.36</v>
       </c>
       <c r="M5">
-        <v>0.06971580000000001</v>
+        <v>0.09295440000000001</v>
       </c>
       <c r="N5">
-        <v>5.2902842</v>
+        <v>5.2670456</v>
       </c>
       <c r="O5">
-        <v>1.32257105</v>
+        <v>1.3167614</v>
       </c>
       <c r="P5">
-        <v>3.96771315</v>
+        <v>3.9502842</v>
       </c>
       <c r="Q5">
-        <v>4.007713150000001</v>
+        <v>3.990284200000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07300768819315753</v>
+        <v>0.07322185450450167</v>
       </c>
       <c r="T5">
-        <v>0.5161197911614087</v>
+        <v>0.5201824469482587</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>76.8835758895401</v>
+        <v>57.66268191715508</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1996,22 +1996,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0718019803243216</v>
+        <v>0.07165475310128039</v>
       </c>
       <c r="C6">
-        <v>43.67712669651375</v>
+        <v>43.33599098982123</v>
       </c>
       <c r="D6">
-        <v>21.22512669651375</v>
+        <v>21.34599098982123</v>
       </c>
       <c r="E6">
-        <v>-9.351999999999999</v>
+        <v>-8.889999999999999</v>
       </c>
       <c r="F6">
-        <v>1.848</v>
+        <v>2.31</v>
       </c>
       <c r="G6">
         <v>24.3</v>
@@ -2032,28 +2032,28 @@
         <v>5.36</v>
       </c>
       <c r="M6">
-        <v>0.09295440000000001</v>
+        <v>0.116193</v>
       </c>
       <c r="N6">
-        <v>5.2670456</v>
+        <v>5.243807</v>
       </c>
       <c r="O6">
-        <v>1.3167614</v>
+        <v>1.31095175</v>
       </c>
       <c r="P6">
-        <v>3.9502842</v>
+        <v>3.93285525</v>
       </c>
       <c r="Q6">
-        <v>3.990284200000001</v>
+        <v>3.97285525</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07322185450450167</v>
+        <v>0.07344052958029515</v>
       </c>
       <c r="T6">
-        <v>0.5201824469482587</v>
+        <v>0.5243306323306212</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>57.66268191715508</v>
+        <v>46.13014553372407</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2078,22 +2078,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07165475310128039</v>
+        <v>0.07150752587823916</v>
       </c>
       <c r="C7">
-        <v>43.33599098982123</v>
+        <v>42.99623966483491</v>
       </c>
       <c r="D7">
-        <v>21.34599098982123</v>
+        <v>21.4682396648349</v>
       </c>
       <c r="E7">
-        <v>-8.889999999999999</v>
+        <v>-8.427999999999999</v>
       </c>
       <c r="F7">
-        <v>2.31</v>
+        <v>2.772</v>
       </c>
       <c r="G7">
         <v>24.3</v>
@@ -2114,28 +2114,28 @@
         <v>5.36</v>
       </c>
       <c r="M7">
-        <v>0.116193</v>
+        <v>0.1394316</v>
       </c>
       <c r="N7">
-        <v>5.243807</v>
+        <v>5.2205684</v>
       </c>
       <c r="O7">
-        <v>1.31095175</v>
+        <v>1.3051421</v>
       </c>
       <c r="P7">
-        <v>3.93285525</v>
+        <v>3.9154263</v>
       </c>
       <c r="Q7">
-        <v>3.97285525</v>
+        <v>3.9554263</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07344052958029515</v>
+        <v>0.0736638573172757</v>
       </c>
       <c r="T7">
-        <v>0.5243306323306212</v>
+        <v>0.5285670769764381</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2152,7 +2152,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>46.13014553372407</v>
+        <v>38.44178794477005</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2160,22 +2160,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07150752587823916</v>
+        <v>0.07136029865519794</v>
       </c>
       <c r="C8">
-        <v>42.99623966483491</v>
+        <v>42.65789664365484</v>
       </c>
       <c r="D8">
-        <v>21.4682396648349</v>
+        <v>21.59189664365484</v>
       </c>
       <c r="E8">
-        <v>-8.427999999999999</v>
+        <v>-7.965999999999999</v>
       </c>
       <c r="F8">
-        <v>2.772</v>
+        <v>3.234</v>
       </c>
       <c r="G8">
         <v>24.3</v>
@@ -2196,28 +2196,28 @@
         <v>5.36</v>
       </c>
       <c r="M8">
-        <v>0.1394316</v>
+        <v>0.1626702</v>
       </c>
       <c r="N8">
-        <v>5.2205684</v>
+        <v>5.1973298</v>
       </c>
       <c r="O8">
-        <v>1.3051421</v>
+        <v>1.29933245</v>
       </c>
       <c r="P8">
-        <v>3.9154263</v>
+        <v>3.89799735</v>
       </c>
       <c r="Q8">
-        <v>3.9554263</v>
+        <v>3.93799735</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0736638573172757</v>
+        <v>0.07389198780128811</v>
       </c>
       <c r="T8">
-        <v>0.5285670769764381</v>
+        <v>0.5328946279587243</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>38.44178794477005</v>
+        <v>32.95010395266005</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2242,22 +2242,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07136029865519794</v>
+        <v>0.07121307143215674</v>
       </c>
       <c r="C9">
-        <v>42.65789664365484</v>
+        <v>42.32098640273904</v>
       </c>
       <c r="D9">
-        <v>21.59189664365484</v>
+        <v>21.71698640273903</v>
       </c>
       <c r="E9">
-        <v>-7.965999999999999</v>
+        <v>-7.504</v>
       </c>
       <c r="F9">
-        <v>3.234</v>
+        <v>3.696</v>
       </c>
       <c r="G9">
         <v>24.3</v>
@@ -2278,28 +2278,28 @@
         <v>5.36</v>
       </c>
       <c r="M9">
-        <v>0.1626702</v>
+        <v>0.1859088</v>
       </c>
       <c r="N9">
-        <v>5.1973298</v>
+        <v>5.1740912</v>
       </c>
       <c r="O9">
-        <v>1.29933245</v>
+        <v>1.2935228</v>
       </c>
       <c r="P9">
-        <v>3.89799735</v>
+        <v>3.8805684</v>
       </c>
       <c r="Q9">
-        <v>3.93799735</v>
+        <v>3.920568400000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07389198780128811</v>
+        <v>0.07412507764364863</v>
       </c>
       <c r="T9">
-        <v>0.5328946279587243</v>
+        <v>0.5373162561362778</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2316,7 +2316,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.95010395266004</v>
+        <v>28.83134095857754</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2324,22 +2324,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07121307143215674</v>
+        <v>0.07106584420911553</v>
       </c>
       <c r="C10">
-        <v>42.32098640273904</v>
+        <v>41.98553398905501</v>
       </c>
       <c r="D10">
-        <v>21.71698640273903</v>
+        <v>21.84353398905501</v>
       </c>
       <c r="E10">
-        <v>-7.504</v>
+        <v>-7.041999999999999</v>
       </c>
       <c r="F10">
-        <v>3.696</v>
+        <v>4.158</v>
       </c>
       <c r="G10">
         <v>24.3</v>
@@ -2360,28 +2360,28 @@
         <v>5.36</v>
       </c>
       <c r="M10">
-        <v>0.1859088</v>
+        <v>0.2091474</v>
       </c>
       <c r="N10">
-        <v>5.1740912</v>
+        <v>5.1508526</v>
       </c>
       <c r="O10">
-        <v>1.2935228</v>
+        <v>1.28771315</v>
       </c>
       <c r="P10">
-        <v>3.8805684</v>
+        <v>3.86313945</v>
       </c>
       <c r="Q10">
-        <v>3.920568400000001</v>
+        <v>3.90313945</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07412507764364863</v>
+        <v>0.07436329033968739</v>
       </c>
       <c r="T10">
-        <v>0.5373162561362778</v>
+        <v>0.5418350629550959</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2398,7 +2398,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.83134095857754</v>
+        <v>25.6278586298467</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2406,22 +2406,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07106584420911553</v>
+        <v>0.07091861698607431</v>
       </c>
       <c r="C11">
-        <v>41.98553398905501</v>
+        <v>41.65156503679932</v>
       </c>
       <c r="D11">
-        <v>21.84353398905501</v>
+        <v>21.97156503679932</v>
       </c>
       <c r="E11">
-        <v>-7.041999999999999</v>
+        <v>-6.579999999999999</v>
       </c>
       <c r="F11">
-        <v>4.158</v>
+        <v>4.62</v>
       </c>
       <c r="G11">
         <v>24.3</v>
@@ -2442,28 +2442,28 @@
         <v>5.36</v>
       </c>
       <c r="M11">
-        <v>0.2091474</v>
+        <v>0.232386</v>
       </c>
       <c r="N11">
-        <v>5.1508526</v>
+        <v>5.127614</v>
       </c>
       <c r="O11">
-        <v>1.28771315</v>
+        <v>1.2819035</v>
       </c>
       <c r="P11">
-        <v>3.86313945</v>
+        <v>3.8457105</v>
       </c>
       <c r="Q11">
-        <v>3.90313945</v>
+        <v>3.8857105</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07436329033968739</v>
+        <v>0.07460679665119367</v>
       </c>
       <c r="T11">
-        <v>0.5418350629550959</v>
+        <v>0.5464542877032211</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2480,7 +2480,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>25.6278586298467</v>
+        <v>23.06507276686203</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2488,22 +2488,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07091861698607431</v>
+        <v>0.07077138976303309</v>
       </c>
       <c r="C12">
-        <v>41.65156503679932</v>
+        <v>41.3191057847086</v>
       </c>
       <c r="D12">
-        <v>21.97156503679932</v>
+        <v>22.10110578470861</v>
       </c>
       <c r="E12">
-        <v>-6.579999999999999</v>
+        <v>-6.117999999999999</v>
       </c>
       <c r="F12">
-        <v>4.62</v>
+        <v>5.082000000000001</v>
       </c>
       <c r="G12">
         <v>24.3</v>
@@ -2524,28 +2524,28 @@
         <v>5.36</v>
       </c>
       <c r="M12">
-        <v>0.232386</v>
+        <v>0.2556246</v>
       </c>
       <c r="N12">
-        <v>5.127614</v>
+        <v>5.1043754</v>
       </c>
       <c r="O12">
-        <v>1.2819035</v>
+        <v>1.27609385</v>
       </c>
       <c r="P12">
-        <v>3.8457105</v>
+        <v>3.82828155</v>
       </c>
       <c r="Q12">
-        <v>3.8857105</v>
+        <v>3.86828155</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07460679665119367</v>
+        <v>0.07485577501464392</v>
       </c>
       <c r="T12">
-        <v>0.5464542877032211</v>
+        <v>0.5511773152546752</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>23.06507276686203</v>
+        <v>20.96824796987457</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2570,22 +2570,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07077138976303309</v>
+        <v>0.07062416253999186</v>
       </c>
       <c r="C13">
-        <v>41.3191057847086</v>
+        <v>40.98818309398665</v>
       </c>
       <c r="D13">
-        <v>22.10110578470861</v>
+        <v>22.23218309398665</v>
       </c>
       <c r="E13">
-        <v>-6.117999999999999</v>
+        <v>-5.655999999999999</v>
       </c>
       <c r="F13">
-        <v>5.082000000000001</v>
+        <v>5.544</v>
       </c>
       <c r="G13">
         <v>24.3</v>
@@ -2606,28 +2606,28 @@
         <v>5.36</v>
       </c>
       <c r="M13">
-        <v>0.2556246</v>
+        <v>0.2788632</v>
       </c>
       <c r="N13">
-        <v>5.1043754</v>
+        <v>5.0811368</v>
       </c>
       <c r="O13">
-        <v>1.27609385</v>
+        <v>1.2702842</v>
       </c>
       <c r="P13">
-        <v>3.82828155</v>
+        <v>3.8108526</v>
       </c>
       <c r="Q13">
-        <v>3.86828155</v>
+        <v>3.850852600000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07485577501464392</v>
+        <v>0.07511041197726348</v>
       </c>
       <c r="T13">
-        <v>0.5511773152546752</v>
+        <v>0.5560076843413894</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2644,7 +2644,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.96824796987457</v>
+        <v>19.22089397238502</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2652,22 +2652,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07062416253999186</v>
+        <v>0.07047693531695065</v>
       </c>
       <c r="C14">
-        <v>40.98818309398665</v>
+        <v>40.65882446687314</v>
       </c>
       <c r="D14">
-        <v>22.23218309398665</v>
+        <v>22.36482446687314</v>
       </c>
       <c r="E14">
-        <v>-5.655999999999999</v>
+        <v>-5.193999999999999</v>
       </c>
       <c r="F14">
-        <v>5.544</v>
+        <v>6.006</v>
       </c>
       <c r="G14">
         <v>24.3</v>
@@ -2688,28 +2688,28 @@
         <v>5.36</v>
       </c>
       <c r="M14">
-        <v>0.2788632</v>
+        <v>0.3021018</v>
       </c>
       <c r="N14">
-        <v>5.0811368</v>
+        <v>5.0578982</v>
       </c>
       <c r="O14">
-        <v>1.2702842</v>
+        <v>1.26447455</v>
       </c>
       <c r="P14">
-        <v>3.8108526</v>
+        <v>3.79342365</v>
       </c>
       <c r="Q14">
-        <v>3.850852600000001</v>
+        <v>3.83342365</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07511041197726348</v>
+        <v>0.07537090266316167</v>
       </c>
       <c r="T14">
-        <v>0.5560076843413894</v>
+        <v>0.5609490963956143</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2726,7 +2726,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>19.22089397238502</v>
+        <v>17.74236366681695</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2734,22 +2734,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07047693531695065</v>
+        <v>0.07032970809390943</v>
       </c>
       <c r="C15">
-        <v>40.65882446687314</v>
+        <v>40.33105806588118</v>
       </c>
       <c r="D15">
-        <v>22.36482446687314</v>
+        <v>22.49905806588118</v>
       </c>
       <c r="E15">
-        <v>-5.193999999999999</v>
+        <v>-4.731999999999998</v>
       </c>
       <c r="F15">
-        <v>6.006</v>
+        <v>6.468000000000001</v>
       </c>
       <c r="G15">
         <v>24.3</v>
@@ -2770,28 +2770,28 @@
         <v>5.36</v>
       </c>
       <c r="M15">
-        <v>0.3021018</v>
+        <v>0.3253404</v>
       </c>
       <c r="N15">
-        <v>5.0578982</v>
+        <v>5.0346596</v>
       </c>
       <c r="O15">
-        <v>1.26447455</v>
+        <v>1.2586649</v>
       </c>
       <c r="P15">
-        <v>3.79342365</v>
+        <v>3.7759947</v>
       </c>
       <c r="Q15">
-        <v>3.83342365</v>
+        <v>3.8159947</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07537090266316167</v>
+        <v>0.07563745127198772</v>
       </c>
       <c r="T15">
-        <v>0.5609490963956143</v>
+        <v>0.5660054250092398</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2808,7 +2808,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.74236366681695</v>
+        <v>16.47505197633002</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2816,22 +2816,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07032970809390943</v>
+        <v>0.07018248087086823</v>
       </c>
       <c r="C16">
-        <v>40.33105806588118</v>
+        <v>40.00491273373165</v>
       </c>
       <c r="D16">
-        <v>22.49905806588118</v>
+        <v>22.63491273373165</v>
       </c>
       <c r="E16">
-        <v>-4.731999999999998</v>
+        <v>-4.269999999999998</v>
       </c>
       <c r="F16">
-        <v>6.468000000000001</v>
+        <v>6.930000000000001</v>
       </c>
       <c r="G16">
         <v>24.3</v>
@@ -2852,28 +2852,28 @@
         <v>5.36</v>
       </c>
       <c r="M16">
-        <v>0.3253404</v>
+        <v>0.3485790000000001</v>
       </c>
       <c r="N16">
-        <v>5.0346596</v>
+        <v>5.011421</v>
       </c>
       <c r="O16">
-        <v>1.2586649</v>
+        <v>1.25285525</v>
       </c>
       <c r="P16">
-        <v>3.7759947</v>
+        <v>3.75856575</v>
       </c>
       <c r="Q16">
-        <v>3.8159947</v>
+        <v>3.79856575</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07563745127198772</v>
+        <v>0.07591027161278614</v>
       </c>
       <c r="T16">
-        <v>0.5660054250092398</v>
+        <v>0.571180726060833</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2890,7 +2890,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.47505197633002</v>
+        <v>15.37671517790802</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2898,22 +2898,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07018248087086823</v>
+        <v>0.07003525364782699</v>
       </c>
       <c r="C17">
-        <v>40.00491273373165</v>
+        <v>39.6804180140144</v>
       </c>
       <c r="D17">
-        <v>22.63491273373165</v>
+        <v>22.77241801401441</v>
       </c>
       <c r="E17">
-        <v>-4.269999999999999</v>
+        <v>-3.807999999999999</v>
       </c>
       <c r="F17">
-        <v>6.930000000000001</v>
+        <v>7.392</v>
       </c>
       <c r="G17">
         <v>24.3</v>
@@ -2934,28 +2934,28 @@
         <v>5.36</v>
       </c>
       <c r="M17">
-        <v>0.348579</v>
+        <v>0.3718176</v>
       </c>
       <c r="N17">
-        <v>5.011421</v>
+        <v>4.9881824</v>
       </c>
       <c r="O17">
-        <v>1.25285525</v>
+        <v>1.2470456</v>
       </c>
       <c r="P17">
-        <v>3.75856575</v>
+        <v>3.7411368</v>
       </c>
       <c r="Q17">
-        <v>3.79856575</v>
+        <v>3.781136800000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07591027161278614</v>
+        <v>0.07618958767598452</v>
       </c>
       <c r="T17">
-        <v>0.571180726060833</v>
+        <v>0.5764792485660355</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>15.37671517790802</v>
+        <v>14.41567047928877</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2980,22 +2980,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07003525364782699</v>
+        <v>0.06988802642478578</v>
       </c>
       <c r="C18">
-        <v>39.6804180140144</v>
+        <v>39.35760417260676</v>
       </c>
       <c r="D18">
-        <v>22.77241801401441</v>
+        <v>22.91160417260675</v>
       </c>
       <c r="E18">
-        <v>-3.807999999999999</v>
+        <v>-3.345999999999998</v>
       </c>
       <c r="F18">
-        <v>7.392</v>
+        <v>7.854000000000001</v>
       </c>
       <c r="G18">
         <v>24.3</v>
@@ -3016,28 +3016,28 @@
         <v>5.36</v>
       </c>
       <c r="M18">
-        <v>0.3718176</v>
+        <v>0.3950562</v>
       </c>
       <c r="N18">
-        <v>4.9881824</v>
+        <v>4.9649438</v>
       </c>
       <c r="O18">
-        <v>1.2470456</v>
+        <v>1.24123595</v>
       </c>
       <c r="P18">
-        <v>3.7411368</v>
+        <v>3.72370785</v>
       </c>
       <c r="Q18">
-        <v>3.781136800000001</v>
+        <v>3.76370785</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07618958767598452</v>
+        <v>0.07647563424672987</v>
       </c>
       <c r="T18">
-        <v>0.5764792485660355</v>
+        <v>0.5819054463123273</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.41567047928877</v>
+        <v>13.56768986286002</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3062,22 +3062,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.06988802642478578</v>
+        <v>0.06994329920174457</v>
       </c>
       <c r="C19">
-        <v>39.35760417260676</v>
+        <v>38.84315119272947</v>
       </c>
       <c r="D19">
-        <v>22.91160417260675</v>
+        <v>22.85915119272947</v>
       </c>
       <c r="E19">
-        <v>-3.345999999999998</v>
+        <v>-2.883999999999999</v>
       </c>
       <c r="F19">
-        <v>7.854000000000001</v>
+        <v>8.316000000000001</v>
       </c>
       <c r="G19">
         <v>24.3</v>
@@ -3098,45 +3098,45 @@
         <v>5.36</v>
       </c>
       <c r="M19">
-        <v>0.3950562</v>
+        <v>0.4307688</v>
       </c>
       <c r="N19">
-        <v>4.9649438</v>
+        <v>4.9292312</v>
       </c>
       <c r="O19">
-        <v>1.24123595</v>
+        <v>1.2323078</v>
       </c>
       <c r="P19">
-        <v>3.72370785</v>
+        <v>3.6969234</v>
       </c>
       <c r="Q19">
-        <v>3.76370785</v>
+        <v>3.7369234</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07647563424672987</v>
+        <v>0.07676865756310314</v>
       </c>
       <c r="T19">
-        <v>0.5819054463123273</v>
+        <v>0.5874639903451139</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.25</v>
       </c>
       <c r="W19">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.56768986286002</v>
+        <v>12.44286958572673</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3144,22 +3144,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.06994329920174458</v>
+        <v>0.06980732197870337</v>
       </c>
       <c r="C20">
-        <v>38.84315119272945</v>
+        <v>38.51062518833063</v>
       </c>
       <c r="D20">
-        <v>22.85915119272946</v>
+        <v>22.98862518833062</v>
       </c>
       <c r="E20">
-        <v>-2.883999999999999</v>
+        <v>-2.421999999999999</v>
       </c>
       <c r="F20">
-        <v>8.316000000000001</v>
+        <v>8.778</v>
       </c>
       <c r="G20">
         <v>24.3</v>
@@ -3180,28 +3180,28 @@
         <v>5.36</v>
       </c>
       <c r="M20">
-        <v>0.4307688</v>
+        <v>0.4547004</v>
       </c>
       <c r="N20">
-        <v>4.9292312</v>
+        <v>4.9052996</v>
       </c>
       <c r="O20">
-        <v>1.2323078</v>
+        <v>1.2263249</v>
       </c>
       <c r="P20">
-        <v>3.6969234</v>
+        <v>3.6789747</v>
       </c>
       <c r="Q20">
-        <v>3.7369234</v>
+        <v>3.7189747</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07676865756310314</v>
+        <v>0.07706891602309057</v>
       </c>
       <c r="T20">
-        <v>0.5874639903451139</v>
+        <v>0.5931597823787103</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.44286958572673</v>
+        <v>11.78798171279374</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3226,22 +3226,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.06980732197870337</v>
+        <v>0.06967134475566214</v>
       </c>
       <c r="C21">
-        <v>38.51062518833063</v>
+        <v>38.17957421724545</v>
       </c>
       <c r="D21">
-        <v>22.98862518833062</v>
+        <v>23.11957421724545</v>
       </c>
       <c r="E21">
-        <v>-2.421999999999999</v>
+        <v>-1.959999999999999</v>
       </c>
       <c r="F21">
-        <v>8.778</v>
+        <v>9.24</v>
       </c>
       <c r="G21">
         <v>24.3</v>
@@ -3262,28 +3262,28 @@
         <v>5.36</v>
       </c>
       <c r="M21">
-        <v>0.4547004</v>
+        <v>0.478632</v>
       </c>
       <c r="N21">
-        <v>4.9052996</v>
+        <v>4.881368</v>
       </c>
       <c r="O21">
-        <v>1.2263249</v>
+        <v>1.220342</v>
       </c>
       <c r="P21">
-        <v>3.6789747</v>
+        <v>3.661026</v>
       </c>
       <c r="Q21">
-        <v>3.7189747</v>
+        <v>3.701026</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07706891602309057</v>
+        <v>0.07737668094457767</v>
       </c>
       <c r="T21">
-        <v>0.5931597823787103</v>
+        <v>0.5989979692131463</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3300,7 +3300,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.78798171279374</v>
+        <v>11.19858262715406</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3308,22 +3308,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.06967134475566214</v>
+        <v>0.06953536753262093</v>
       </c>
       <c r="C22">
-        <v>38.17957421724545</v>
+        <v>37.85002363036853</v>
       </c>
       <c r="D22">
-        <v>23.11957421724545</v>
+        <v>23.25202363036852</v>
       </c>
       <c r="E22">
-        <v>-1.959999999999999</v>
+        <v>-1.497999999999998</v>
       </c>
       <c r="F22">
-        <v>9.24</v>
+        <v>9.702000000000002</v>
       </c>
       <c r="G22">
         <v>24.3</v>
@@ -3344,28 +3344,28 @@
         <v>5.36</v>
       </c>
       <c r="M22">
-        <v>0.478632</v>
+        <v>0.5025636000000001</v>
       </c>
       <c r="N22">
-        <v>4.881368</v>
+        <v>4.8574364</v>
       </c>
       <c r="O22">
-        <v>1.220342</v>
+        <v>1.2143591</v>
       </c>
       <c r="P22">
-        <v>3.661026</v>
+        <v>3.6430773</v>
       </c>
       <c r="Q22">
-        <v>3.701026</v>
+        <v>3.6830773</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07737668094457767</v>
+        <v>0.07769223738306447</v>
       </c>
       <c r="T22">
-        <v>0.5989979692131463</v>
+        <v>0.6049839582459225</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3382,7 +3382,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>11.19858262715406</v>
+        <v>10.66531678776577</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3390,22 +3390,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.06953536753262093</v>
+        <v>0.06939939030957971</v>
       </c>
       <c r="C23">
-        <v>37.85002363036853</v>
+        <v>37.52199936287136</v>
       </c>
       <c r="D23">
-        <v>23.25202363036852</v>
+        <v>23.38599936287136</v>
       </c>
       <c r="E23">
-        <v>-1.497999999999999</v>
+        <v>-1.035999999999998</v>
       </c>
       <c r="F23">
-        <v>9.702</v>
+        <v>10.164</v>
       </c>
       <c r="G23">
         <v>24.3</v>
@@ -3426,28 +3426,28 @@
         <v>5.36</v>
       </c>
       <c r="M23">
-        <v>0.5025636</v>
+        <v>0.5264952000000001</v>
       </c>
       <c r="N23">
-        <v>4.8574364</v>
+        <v>4.8335048</v>
       </c>
       <c r="O23">
-        <v>1.2143591</v>
+        <v>1.2083762</v>
       </c>
       <c r="P23">
-        <v>3.6430773</v>
+        <v>3.6251286</v>
       </c>
       <c r="Q23">
-        <v>3.6830773</v>
+        <v>3.6651286</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07769223738306447</v>
+        <v>0.07801588501228168</v>
       </c>
       <c r="T23">
-        <v>0.6049839582459225</v>
+        <v>0.6111234341769751</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3464,7 +3464,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.66531678776577</v>
+        <v>10.18052966104914</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3472,22 +3472,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.06939939030957971</v>
+        <v>0.06955666308653849</v>
       </c>
       <c r="C24">
-        <v>37.52199936287136</v>
+        <v>36.90518043698277</v>
       </c>
       <c r="D24">
-        <v>23.38599936287136</v>
+        <v>23.23118043698277</v>
       </c>
       <c r="E24">
-        <v>-1.035999999999998</v>
+        <v>-0.5739999999999981</v>
       </c>
       <c r="F24">
-        <v>10.164</v>
+        <v>10.626</v>
       </c>
       <c r="G24">
         <v>24.3</v>
@@ -3508,45 +3508,45 @@
         <v>5.36</v>
       </c>
       <c r="M24">
-        <v>0.5264952000000001</v>
+        <v>0.5684910000000001</v>
       </c>
       <c r="N24">
-        <v>4.8335048</v>
+        <v>4.791509</v>
       </c>
       <c r="O24">
-        <v>1.2083762</v>
+        <v>1.19787725</v>
       </c>
       <c r="P24">
-        <v>3.6251286</v>
+        <v>3.59363175</v>
       </c>
       <c r="Q24">
-        <v>3.6651286</v>
+        <v>3.63363175</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07801588501228168</v>
+        <v>0.07834793907342662</v>
       </c>
       <c r="T24">
-        <v>0.6111234341769751</v>
+        <v>0.6174223770153279</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.25</v>
       </c>
       <c r="W24">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>10.18052966104914</v>
+        <v>9.428469404089071</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3554,22 +3554,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.06955666308653849</v>
+        <v>0.06943343586349728</v>
       </c>
       <c r="C25">
-        <v>36.90518043698277</v>
+        <v>36.56431025787523</v>
       </c>
       <c r="D25">
-        <v>23.23118043698277</v>
+        <v>23.35231025787523</v>
       </c>
       <c r="E25">
-        <v>-0.5739999999999981</v>
+        <v>-0.1119999999999983</v>
       </c>
       <c r="F25">
-        <v>10.626</v>
+        <v>11.088</v>
       </c>
       <c r="G25">
         <v>24.3</v>
@@ -3590,28 +3590,28 @@
         <v>5.36</v>
       </c>
       <c r="M25">
-        <v>0.5684910000000001</v>
+        <v>0.5932080000000001</v>
       </c>
       <c r="N25">
-        <v>4.791509</v>
+        <v>4.766792000000001</v>
       </c>
       <c r="O25">
-        <v>1.19787725</v>
+        <v>1.191698</v>
       </c>
       <c r="P25">
-        <v>3.59363175</v>
+        <v>3.575094</v>
       </c>
       <c r="Q25">
-        <v>3.63363175</v>
+        <v>3.615094</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07834793907342662</v>
+        <v>0.07868873139933852</v>
       </c>
       <c r="T25">
-        <v>0.6174223770153279</v>
+        <v>0.6238870815073214</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.428469404089071</v>
+        <v>9.035616512252027</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3636,22 +3636,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.06943343586349728</v>
+        <v>0.06931020864045606</v>
       </c>
       <c r="C26">
-        <v>36.56431025787523</v>
+        <v>36.22470986685714</v>
       </c>
       <c r="D26">
-        <v>23.35231025787523</v>
+        <v>23.47470986685713</v>
       </c>
       <c r="E26">
-        <v>-0.1119999999999983</v>
+        <v>0.3500000000000014</v>
       </c>
       <c r="F26">
-        <v>11.088</v>
+        <v>11.55</v>
       </c>
       <c r="G26">
         <v>24.3</v>
@@ -3672,28 +3672,28 @@
         <v>5.36</v>
       </c>
       <c r="M26">
-        <v>0.5932080000000001</v>
+        <v>0.6179250000000001</v>
       </c>
       <c r="N26">
-        <v>4.766792000000001</v>
+        <v>4.742075</v>
       </c>
       <c r="O26">
-        <v>1.191698</v>
+        <v>1.18551875</v>
       </c>
       <c r="P26">
-        <v>3.575094</v>
+        <v>3.55655625</v>
       </c>
       <c r="Q26">
-        <v>3.615094</v>
+        <v>3.59655625</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07868873139933852</v>
+        <v>0.07903861152060808</v>
       </c>
       <c r="T26">
-        <v>0.6238870815073214</v>
+        <v>0.6305241781191013</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>9.035616512252027</v>
+        <v>8.674191851761943</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3718,22 +3718,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06931020864045606</v>
+        <v>0.06918698141741485</v>
       </c>
       <c r="C27">
-        <v>36.22470986685714</v>
+        <v>35.8863993356672</v>
       </c>
       <c r="D27">
-        <v>23.47470986685713</v>
+        <v>23.5983993356672</v>
       </c>
       <c r="E27">
-        <v>0.3500000000000014</v>
+        <v>0.8120000000000012</v>
       </c>
       <c r="F27">
-        <v>11.55</v>
+        <v>12.012</v>
       </c>
       <c r="G27">
         <v>24.3</v>
@@ -3754,28 +3754,28 @@
         <v>5.36</v>
       </c>
       <c r="M27">
-        <v>0.6179250000000001</v>
+        <v>0.642642</v>
       </c>
       <c r="N27">
-        <v>4.742075</v>
+        <v>4.717358</v>
       </c>
       <c r="O27">
-        <v>1.18551875</v>
+        <v>1.1793395</v>
       </c>
       <c r="P27">
-        <v>3.55655625</v>
+        <v>3.5380185</v>
       </c>
       <c r="Q27">
-        <v>3.59655625</v>
+        <v>3.5780185</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.07903861152060808</v>
+        <v>0.07939794786137142</v>
       </c>
       <c r="T27">
-        <v>0.6305241781191013</v>
+        <v>0.637340655720389</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.674191851761943</v>
+        <v>8.340569088232639</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3800,22 +3800,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.06918698141741485</v>
+        <v>0.06906375419437363</v>
       </c>
       <c r="C28">
-        <v>35.8863993356672</v>
+        <v>35.54939916132111</v>
       </c>
       <c r="D28">
-        <v>23.5983993356672</v>
+        <v>23.7233991613211</v>
       </c>
       <c r="E28">
-        <v>0.8120000000000012</v>
+        <v>1.274000000000003</v>
       </c>
       <c r="F28">
-        <v>12.012</v>
+        <v>12.474</v>
       </c>
       <c r="G28">
         <v>24.3</v>
@@ -3836,28 +3836,28 @@
         <v>5.36</v>
       </c>
       <c r="M28">
-        <v>0.642642</v>
+        <v>0.6673590000000001</v>
       </c>
       <c r="N28">
-        <v>4.717358</v>
+        <v>4.692641</v>
       </c>
       <c r="O28">
-        <v>1.1793395</v>
+        <v>1.17316025</v>
       </c>
       <c r="P28">
-        <v>3.5380185</v>
+        <v>3.51948075</v>
       </c>
       <c r="Q28">
-        <v>3.5780185</v>
+        <v>3.55948075</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.07939794786137142</v>
+        <v>0.07976712903338853</v>
       </c>
       <c r="T28">
-        <v>0.637340655720389</v>
+        <v>0.6443438861326708</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.340569088232639</v>
+        <v>8.0316591220018</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3882,22 +3882,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.06906375419437363</v>
+        <v>0.06894052697133241</v>
       </c>
       <c r="C29">
-        <v>35.54939916132111</v>
+        <v>35.21373027743483</v>
       </c>
       <c r="D29">
-        <v>23.7233991613211</v>
+        <v>23.84973027743483</v>
       </c>
       <c r="E29">
-        <v>1.274000000000003</v>
+        <v>1.736000000000002</v>
       </c>
       <c r="F29">
-        <v>12.474</v>
+        <v>12.936</v>
       </c>
       <c r="G29">
         <v>24.3</v>
@@ -3918,28 +3918,28 @@
         <v>5.36</v>
       </c>
       <c r="M29">
-        <v>0.6673590000000001</v>
+        <v>0.692076</v>
       </c>
       <c r="N29">
-        <v>4.692641</v>
+        <v>4.667924</v>
       </c>
       <c r="O29">
-        <v>1.17316025</v>
+        <v>1.166981</v>
       </c>
       <c r="P29">
-        <v>3.51948075</v>
+        <v>3.500943</v>
       </c>
       <c r="Q29">
-        <v>3.55948075</v>
+        <v>3.540943</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.07976712903338853</v>
+        <v>0.08014656523796168</v>
       </c>
       <c r="T29">
-        <v>0.6443438861326708</v>
+        <v>0.6515416507230715</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3956,7 +3956,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.0316591220018</v>
+        <v>7.74481415335888</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3964,22 +3964,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.06894052697133241</v>
+        <v>0.06899129974829118</v>
       </c>
       <c r="C30">
-        <v>35.21373027743483</v>
+        <v>34.69951599668963</v>
       </c>
       <c r="D30">
-        <v>23.84973027743483</v>
+        <v>23.79751599668963</v>
       </c>
       <c r="E30">
-        <v>1.736000000000002</v>
+        <v>2.198000000000004</v>
       </c>
       <c r="F30">
-        <v>12.936</v>
+        <v>13.398</v>
       </c>
       <c r="G30">
         <v>24.3</v>
@@ -4000,45 +4000,45 @@
         <v>5.36</v>
       </c>
       <c r="M30">
-        <v>0.692076</v>
+        <v>0.7275114000000001</v>
       </c>
       <c r="N30">
-        <v>4.667924</v>
+        <v>4.6324886</v>
       </c>
       <c r="O30">
-        <v>1.166981</v>
+        <v>1.15812215</v>
       </c>
       <c r="P30">
-        <v>3.500943</v>
+        <v>3.47436645</v>
       </c>
       <c r="Q30">
-        <v>3.540943</v>
+        <v>3.51436645</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08014656523796168</v>
+        <v>0.08053668978632562</v>
       </c>
       <c r="T30">
-        <v>0.6515416507230715</v>
+        <v>0.658942169245596</v>
       </c>
       <c r="U30">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y30">
-        <v>7.74481415335888</v>
+        <v>7.36758214372998</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4046,22 +4046,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06899129974829118</v>
+        <v>0.06887407252524998</v>
       </c>
       <c r="C31">
-        <v>34.69951599668964</v>
+        <v>34.35841865539966</v>
       </c>
       <c r="D31">
-        <v>23.79751599668963</v>
+        <v>23.91841865539966</v>
       </c>
       <c r="E31">
-        <v>2.198</v>
+        <v>2.660000000000002</v>
       </c>
       <c r="F31">
-        <v>13.398</v>
+        <v>13.86</v>
       </c>
       <c r="G31">
         <v>24.3</v>
@@ -4082,28 +4082,28 @@
         <v>5.36</v>
       </c>
       <c r="M31">
-        <v>0.7275114</v>
+        <v>0.7525980000000001</v>
       </c>
       <c r="N31">
-        <v>4.6324886</v>
+        <v>4.607402</v>
       </c>
       <c r="O31">
-        <v>1.15812215</v>
+        <v>1.1518505</v>
       </c>
       <c r="P31">
-        <v>3.47436645</v>
+        <v>3.4555515</v>
       </c>
       <c r="Q31">
-        <v>3.51436645</v>
+        <v>3.4955515</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08053668978632562</v>
+        <v>0.08093796075035711</v>
       </c>
       <c r="T31">
-        <v>0.658942169245596</v>
+        <v>0.6665541311544786</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.367582143729981</v>
+        <v>7.121996072272315</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4128,22 +4128,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06887407252524998</v>
+        <v>0.06875684530220876</v>
       </c>
       <c r="C32">
-        <v>34.35841865539966</v>
+        <v>34.01855607287139</v>
       </c>
       <c r="D32">
-        <v>23.91841865539966</v>
+        <v>24.04055607287139</v>
       </c>
       <c r="E32">
-        <v>2.660000000000002</v>
+        <v>3.122000000000002</v>
       </c>
       <c r="F32">
-        <v>13.86</v>
+        <v>14.322</v>
       </c>
       <c r="G32">
         <v>24.3</v>
@@ -4164,28 +4164,28 @@
         <v>5.36</v>
       </c>
       <c r="M32">
-        <v>0.7525980000000001</v>
+        <v>0.7776846000000001</v>
       </c>
       <c r="N32">
-        <v>4.607402</v>
+        <v>4.582315400000001</v>
       </c>
       <c r="O32">
-        <v>1.1518505</v>
+        <v>1.14557885</v>
       </c>
       <c r="P32">
-        <v>3.4555515</v>
+        <v>3.43673655</v>
       </c>
       <c r="Q32">
-        <v>3.4955515</v>
+        <v>3.47673655</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08093796075035711</v>
+        <v>0.08135086275682429</v>
       </c>
       <c r="T32">
-        <v>0.6665541311544786</v>
+        <v>0.6743867296404301</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.121996072272315</v>
+        <v>6.892254263489337</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4210,22 +4210,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06875684530220876</v>
+        <v>0.06863961807916755</v>
       </c>
       <c r="C33">
-        <v>34.01855607287139</v>
+        <v>33.67994726177046</v>
       </c>
       <c r="D33">
-        <v>24.04055607287139</v>
+        <v>24.16394726177046</v>
       </c>
       <c r="E33">
-        <v>3.122000000000002</v>
+        <v>3.584000000000001</v>
       </c>
       <c r="F33">
-        <v>14.322</v>
+        <v>14.784</v>
       </c>
       <c r="G33">
         <v>24.3</v>
@@ -4246,28 +4246,28 @@
         <v>5.36</v>
       </c>
       <c r="M33">
-        <v>0.7776846000000001</v>
+        <v>0.8027712</v>
       </c>
       <c r="N33">
-        <v>4.582315400000001</v>
+        <v>4.557228800000001</v>
       </c>
       <c r="O33">
-        <v>1.14557885</v>
+        <v>1.1393072</v>
       </c>
       <c r="P33">
-        <v>3.43673655</v>
+        <v>3.417921600000001</v>
       </c>
       <c r="Q33">
-        <v>3.47673655</v>
+        <v>3.457921600000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08135086275682429</v>
+        <v>0.08177590893995228</v>
       </c>
       <c r="T33">
-        <v>0.6743867296404301</v>
+        <v>0.6824496986700862</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4284,7 +4284,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.892254263489337</v>
+        <v>6.676871317755296</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4292,22 +4292,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06863961807916755</v>
+        <v>0.06852239085612633</v>
       </c>
       <c r="C34">
-        <v>33.67994726177046</v>
+        <v>33.34261162711598</v>
       </c>
       <c r="D34">
-        <v>24.16394726177046</v>
+        <v>24.28861162711598</v>
       </c>
       <c r="E34">
-        <v>3.584000000000001</v>
+        <v>4.046000000000003</v>
       </c>
       <c r="F34">
-        <v>14.784</v>
+        <v>15.246</v>
       </c>
       <c r="G34">
         <v>24.3</v>
@@ -4328,28 +4328,28 @@
         <v>5.36</v>
       </c>
       <c r="M34">
-        <v>0.8027712</v>
+        <v>0.8278578000000001</v>
       </c>
       <c r="N34">
-        <v>4.557228800000001</v>
+        <v>4.5321422</v>
       </c>
       <c r="O34">
-        <v>1.1393072</v>
+        <v>1.13303555</v>
       </c>
       <c r="P34">
-        <v>3.417921600000001</v>
+        <v>3.39910665</v>
       </c>
       <c r="Q34">
-        <v>3.457921600000001</v>
+        <v>3.43910665</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08177590893995228</v>
+        <v>0.08221364306884527</v>
       </c>
       <c r="T34">
-        <v>0.6824496986700862</v>
+        <v>0.6907533533424186</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.676871317755296</v>
+        <v>6.474541883883923</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4374,22 +4374,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06852239085612633</v>
+        <v>0.06840516363308512</v>
       </c>
       <c r="C35">
-        <v>33.34261162711598</v>
+        <v>33.00656897645389</v>
       </c>
       <c r="D35">
-        <v>24.28861162711598</v>
+        <v>24.4145689764539</v>
       </c>
       <c r="E35">
-        <v>4.046000000000003</v>
+        <v>4.508000000000003</v>
       </c>
       <c r="F35">
-        <v>15.246</v>
+        <v>15.708</v>
       </c>
       <c r="G35">
         <v>24.3</v>
@@ -4410,28 +4410,28 @@
         <v>5.36</v>
       </c>
       <c r="M35">
-        <v>0.8278578000000001</v>
+        <v>0.8529444000000002</v>
       </c>
       <c r="N35">
-        <v>4.5321422</v>
+        <v>4.5070556</v>
       </c>
       <c r="O35">
-        <v>1.13303555</v>
+        <v>1.1267639</v>
       </c>
       <c r="P35">
-        <v>3.39910665</v>
+        <v>3.3802917</v>
       </c>
       <c r="Q35">
-        <v>3.43910665</v>
+        <v>3.4202917</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08221364306884527</v>
+        <v>0.08266464186831078</v>
       </c>
       <c r="T35">
-        <v>0.6907533533424186</v>
+        <v>0.6993086339139125</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4448,7 +4448,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.474541883883923</v>
+        <v>6.284114181416748</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4456,22 +4456,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06840516363308512</v>
+        <v>0.06855043641004389</v>
       </c>
       <c r="C36">
-        <v>33.00656897645389</v>
+        <v>32.38866989084799</v>
       </c>
       <c r="D36">
-        <v>24.4145689764539</v>
+        <v>24.25866989084799</v>
       </c>
       <c r="E36">
-        <v>4.508000000000003</v>
+        <v>4.970000000000002</v>
       </c>
       <c r="F36">
-        <v>15.708</v>
+        <v>16.17</v>
       </c>
       <c r="G36">
         <v>24.3</v>
@@ -4492,45 +4492,45 @@
         <v>5.36</v>
       </c>
       <c r="M36">
-        <v>0.8529444000000002</v>
+        <v>0.8942010000000001</v>
       </c>
       <c r="N36">
-        <v>4.5070556</v>
+        <v>4.465799000000001</v>
       </c>
       <c r="O36">
-        <v>1.1267639</v>
+        <v>1.11644975</v>
       </c>
       <c r="P36">
-        <v>3.3802917</v>
+        <v>3.34934925</v>
       </c>
       <c r="Q36">
-        <v>3.4202917</v>
+        <v>3.38934925</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08266464186831078</v>
+        <v>0.08312951755391369</v>
       </c>
       <c r="T36">
-        <v>0.6993086339139125</v>
+        <v>0.7081271538876062</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.284114181416748</v>
+        <v>5.994178042744305</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4538,22 +4538,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06855043641004389</v>
+        <v>0.06844070918700268</v>
       </c>
       <c r="C37">
-        <v>32.38866989084799</v>
+        <v>32.04423849083356</v>
       </c>
       <c r="D37">
-        <v>24.25866989084799</v>
+        <v>24.37623849083356</v>
       </c>
       <c r="E37">
-        <v>4.970000000000002</v>
+        <v>5.432000000000002</v>
       </c>
       <c r="F37">
-        <v>16.17</v>
+        <v>16.632</v>
       </c>
       <c r="G37">
         <v>24.3</v>
@@ -4574,28 +4574,28 @@
         <v>5.36</v>
       </c>
       <c r="M37">
-        <v>0.8942010000000001</v>
+        <v>0.9197496000000002</v>
       </c>
       <c r="N37">
-        <v>4.465799000000001</v>
+        <v>4.4402504</v>
       </c>
       <c r="O37">
-        <v>1.11644975</v>
+        <v>1.1100626</v>
       </c>
       <c r="P37">
-        <v>3.34934925</v>
+        <v>3.3301878</v>
       </c>
       <c r="Q37">
-        <v>3.38934925</v>
+        <v>3.3701878</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08312951755391369</v>
+        <v>0.08360892060469169</v>
       </c>
       <c r="T37">
-        <v>0.7081271538876062</v>
+        <v>0.7172212526104778</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4612,7 +4612,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.994178042744305</v>
+        <v>5.827673097112518</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4620,22 +4620,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06844070918700268</v>
+        <v>0.06833098196396147</v>
       </c>
       <c r="C38">
-        <v>32.04423849083356</v>
+        <v>31.7009522229766</v>
       </c>
       <c r="D38">
-        <v>24.37623849083356</v>
+        <v>24.49495222297661</v>
       </c>
       <c r="E38">
-        <v>5.432000000000002</v>
+        <v>5.894000000000002</v>
       </c>
       <c r="F38">
-        <v>16.632</v>
+        <v>17.094</v>
       </c>
       <c r="G38">
         <v>24.3</v>
@@ -4656,28 +4656,28 @@
         <v>5.36</v>
       </c>
       <c r="M38">
-        <v>0.9197496000000002</v>
+        <v>0.9452982000000001</v>
       </c>
       <c r="N38">
-        <v>4.4402504</v>
+        <v>4.4147018</v>
       </c>
       <c r="O38">
-        <v>1.1100626</v>
+        <v>1.10367545</v>
       </c>
       <c r="P38">
-        <v>3.3301878</v>
+        <v>3.311026350000001</v>
       </c>
       <c r="Q38">
-        <v>3.3701878</v>
+        <v>3.351026350000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08360892060469169</v>
+        <v>0.08410354279993884</v>
       </c>
       <c r="T38">
-        <v>0.7172212526104778</v>
+        <v>0.7266040528801073</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.827673097112518</v>
+        <v>5.67016841881218</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4702,22 +4702,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.06833098196396147</v>
+        <v>0.06822125474092025</v>
       </c>
       <c r="C39">
-        <v>31.7009522229766</v>
+        <v>31.3588278997401</v>
       </c>
       <c r="D39">
-        <v>24.49495222297661</v>
+        <v>24.6148278997401</v>
       </c>
       <c r="E39">
-        <v>5.894000000000002</v>
+        <v>6.356000000000002</v>
       </c>
       <c r="F39">
-        <v>17.094</v>
+        <v>17.556</v>
       </c>
       <c r="G39">
         <v>24.3</v>
@@ -4738,28 +4738,28 @@
         <v>5.36</v>
       </c>
       <c r="M39">
-        <v>0.9452982000000001</v>
+        <v>0.9708468000000001</v>
       </c>
       <c r="N39">
-        <v>4.4147018</v>
+        <v>4.3891532</v>
       </c>
       <c r="O39">
-        <v>1.10367545</v>
+        <v>1.0972883</v>
       </c>
       <c r="P39">
-        <v>3.311026350000001</v>
+        <v>3.2918649</v>
       </c>
       <c r="Q39">
-        <v>3.351026350000001</v>
+        <v>3.3318649</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08410354279993884</v>
+        <v>0.08461412054987137</v>
       </c>
       <c r="T39">
-        <v>0.7266040528801073</v>
+        <v>0.7362895241261764</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4776,7 +4776,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.67016841881218</v>
+        <v>5.520953460422385</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4784,22 +4784,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06822125474092025</v>
+        <v>0.06811152751787902</v>
       </c>
       <c r="C40">
-        <v>31.3588278997401</v>
+        <v>31.01788266431917</v>
       </c>
       <c r="D40">
-        <v>24.6148278997401</v>
+        <v>24.73588266431917</v>
       </c>
       <c r="E40">
-        <v>6.356000000000002</v>
+        <v>6.818000000000001</v>
       </c>
       <c r="F40">
-        <v>17.556</v>
+        <v>18.018</v>
       </c>
       <c r="G40">
         <v>24.3</v>
@@ -4820,28 +4820,28 @@
         <v>5.36</v>
       </c>
       <c r="M40">
-        <v>0.9708468000000001</v>
+        <v>0.9963954</v>
       </c>
       <c r="N40">
-        <v>4.3891532</v>
+        <v>4.3636046</v>
       </c>
       <c r="O40">
-        <v>1.0972883</v>
+        <v>1.09090115</v>
       </c>
       <c r="P40">
-        <v>3.2918649</v>
+        <v>3.27270345</v>
       </c>
       <c r="Q40">
-        <v>3.3318649</v>
+        <v>3.31270345</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08461412054987137</v>
+        <v>0.08514143855390005</v>
       </c>
       <c r="T40">
-        <v>0.7362895241261764</v>
+        <v>0.746292551806543</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.520953460422385</v>
+        <v>5.379390551180786</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4866,22 +4866,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06811152751787902</v>
+        <v>0.06800180029483782</v>
       </c>
       <c r="C41">
-        <v>31.01788266431917</v>
+        <v>30.67813399881387</v>
       </c>
       <c r="D41">
-        <v>24.73588266431917</v>
+        <v>24.85813399881387</v>
       </c>
       <c r="E41">
-        <v>6.818000000000001</v>
+        <v>7.280000000000001</v>
       </c>
       <c r="F41">
-        <v>18.018</v>
+        <v>18.48</v>
       </c>
       <c r="G41">
         <v>24.3</v>
@@ -4902,28 +4902,28 @@
         <v>5.36</v>
       </c>
       <c r="M41">
-        <v>0.9963954</v>
+        <v>1.021944</v>
       </c>
       <c r="N41">
-        <v>4.3636046</v>
+        <v>4.338056</v>
       </c>
       <c r="O41">
-        <v>1.09090115</v>
+        <v>1.084514</v>
       </c>
       <c r="P41">
-        <v>3.27270345</v>
+        <v>3.253542</v>
       </c>
       <c r="Q41">
-        <v>3.31270345</v>
+        <v>3.293542</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08514143855390005</v>
+        <v>0.0856863338247297</v>
       </c>
       <c r="T41">
-        <v>0.746292551806543</v>
+        <v>0.7566290137429217</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4940,7 +4940,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.379390551180786</v>
+        <v>5.244905787401267</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4948,22 +4948,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06800180029483782</v>
+        <v>0.06789207307179661</v>
       </c>
       <c r="C42">
-        <v>30.67813399881387</v>
+        <v>30.33959973264571</v>
       </c>
       <c r="D42">
-        <v>24.85813399881387</v>
+        <v>24.98159973264572</v>
       </c>
       <c r="E42">
-        <v>7.280000000000001</v>
+        <v>7.742000000000004</v>
       </c>
       <c r="F42">
-        <v>18.48</v>
+        <v>18.942</v>
       </c>
       <c r="G42">
         <v>24.3</v>
@@ -4984,28 +4984,28 @@
         <v>5.36</v>
       </c>
       <c r="M42">
-        <v>1.021944</v>
+        <v>1.0474926</v>
       </c>
       <c r="N42">
-        <v>4.338056</v>
+        <v>4.3125074</v>
       </c>
       <c r="O42">
-        <v>1.084514</v>
+        <v>1.07812685</v>
       </c>
       <c r="P42">
-        <v>3.253542</v>
+        <v>3.23438055</v>
       </c>
       <c r="Q42">
-        <v>3.293542</v>
+        <v>3.27438055</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.0856863338247297</v>
+        <v>0.08624970012168917</v>
       </c>
       <c r="T42">
-        <v>0.7566290137429217</v>
+        <v>0.7673158642195167</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.244905787401267</v>
+        <v>5.116981256001235</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5030,22 +5030,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06789207307179661</v>
+        <v>0.06778234584875538</v>
       </c>
       <c r="C43">
-        <v>30.33959973264571</v>
+        <v>30.00229805122603</v>
       </c>
       <c r="D43">
-        <v>24.98159973264572</v>
+        <v>25.10629805122603</v>
       </c>
       <c r="E43">
-        <v>7.742000000000004</v>
+        <v>8.204000000000004</v>
       </c>
       <c r="F43">
-        <v>18.942</v>
+        <v>19.404</v>
       </c>
       <c r="G43">
         <v>24.3</v>
@@ -5066,28 +5066,28 @@
         <v>5.36</v>
       </c>
       <c r="M43">
-        <v>1.0474926</v>
+        <v>1.0730412</v>
       </c>
       <c r="N43">
-        <v>4.3125074</v>
+        <v>4.2869588</v>
       </c>
       <c r="O43">
-        <v>1.07812685</v>
+        <v>1.0717397</v>
       </c>
       <c r="P43">
-        <v>3.23438055</v>
+        <v>3.2152191</v>
       </c>
       <c r="Q43">
-        <v>3.27438055</v>
+        <v>3.2552191</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08624970012168917</v>
+        <v>0.0868324928426817</v>
       </c>
       <c r="T43">
-        <v>0.7673158642195167</v>
+        <v>0.7783712267815114</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.116981256001235</v>
+        <v>4.995148368953586</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5112,22 +5112,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06778234584875539</v>
+        <v>0.06767261862571416</v>
       </c>
       <c r="C44">
-        <v>30.00229805122602</v>
+        <v>29.66624750488529</v>
       </c>
       <c r="D44">
-        <v>25.10629805122601</v>
+        <v>25.23224750488529</v>
       </c>
       <c r="E44">
-        <v>8.204000000000001</v>
+        <v>8.666</v>
       </c>
       <c r="F44">
-        <v>19.404</v>
+        <v>19.866</v>
       </c>
       <c r="G44">
         <v>24.3</v>
@@ -5148,28 +5148,28 @@
         <v>5.36</v>
       </c>
       <c r="M44">
-        <v>1.0730412</v>
+        <v>1.0985898</v>
       </c>
       <c r="N44">
-        <v>4.286958800000001</v>
+        <v>4.2614102</v>
       </c>
       <c r="O44">
-        <v>1.0717397</v>
+        <v>1.06535255</v>
       </c>
       <c r="P44">
-        <v>3.215219100000001</v>
+        <v>3.19605765</v>
       </c>
       <c r="Q44">
-        <v>3.255219100000001</v>
+        <v>3.23605765</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.0868324928426817</v>
+        <v>0.08743573443107748</v>
       </c>
       <c r="T44">
-        <v>0.7783712267815114</v>
+        <v>0.7898144968018216</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.995148368953588</v>
+        <v>4.878982127815132</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5194,22 +5194,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06767261862571416</v>
+        <v>0.06756289140267295</v>
       </c>
       <c r="C45">
-        <v>29.66624750488529</v>
+        <v>29.33146701807275</v>
       </c>
       <c r="D45">
-        <v>25.23224750488529</v>
+        <v>25.35946701807275</v>
       </c>
       <c r="E45">
-        <v>8.666</v>
+        <v>9.128000000000004</v>
       </c>
       <c r="F45">
-        <v>19.866</v>
+        <v>20.328</v>
       </c>
       <c r="G45">
         <v>24.3</v>
@@ -5230,28 +5230,28 @@
         <v>5.36</v>
       </c>
       <c r="M45">
-        <v>1.0985898</v>
+        <v>1.1241384</v>
       </c>
       <c r="N45">
-        <v>4.2614102</v>
+        <v>4.2358616</v>
       </c>
       <c r="O45">
-        <v>1.06535255</v>
+        <v>1.0589654</v>
       </c>
       <c r="P45">
-        <v>3.19605765</v>
+        <v>3.1768962</v>
       </c>
       <c r="Q45">
-        <v>3.23605765</v>
+        <v>3.2168962</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08743573443107748</v>
+        <v>0.08806052036191599</v>
       </c>
       <c r="T45">
-        <v>0.7898144968018216</v>
+        <v>0.8016664550371432</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5268,7 +5268,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.878982127815132</v>
+        <v>4.768096170364787</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5276,22 +5276,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06756289140267295</v>
+        <v>0.06745316417963174</v>
       </c>
       <c r="C46">
-        <v>29.33146701807275</v>
+        <v>28.99797589883558</v>
       </c>
       <c r="D46">
-        <v>25.35946701807275</v>
+        <v>25.48797589883559</v>
       </c>
       <c r="E46">
-        <v>9.128000000000004</v>
+        <v>9.590000000000003</v>
       </c>
       <c r="F46">
-        <v>20.328</v>
+        <v>20.79</v>
       </c>
       <c r="G46">
         <v>24.3</v>
@@ -5312,28 +5312,28 @@
         <v>5.36</v>
       </c>
       <c r="M46">
-        <v>1.1241384</v>
+        <v>1.149687</v>
       </c>
       <c r="N46">
-        <v>4.2358616</v>
+        <v>4.210313</v>
       </c>
       <c r="O46">
-        <v>1.0589654</v>
+        <v>1.05257825</v>
       </c>
       <c r="P46">
-        <v>3.1768962</v>
+        <v>3.15773475</v>
       </c>
       <c r="Q46">
-        <v>3.2168962</v>
+        <v>3.19773475</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08806052036191599</v>
+        <v>0.08870802578114861</v>
       </c>
       <c r="T46">
-        <v>0.8016664550371432</v>
+        <v>0.8139493935719307</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5350,7 +5350,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.768096170364787</v>
+        <v>4.662138477690014</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5358,22 +5358,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06745316417963174</v>
+        <v>0.06734343695659052</v>
       </c>
       <c r="C47">
-        <v>28.99797589883558</v>
+        <v>28.6657938485878</v>
       </c>
       <c r="D47">
-        <v>25.48797589883559</v>
+        <v>25.6177938485878</v>
       </c>
       <c r="E47">
-        <v>9.590000000000003</v>
+        <v>10.052</v>
       </c>
       <c r="F47">
-        <v>20.79</v>
+        <v>21.252</v>
       </c>
       <c r="G47">
         <v>24.3</v>
@@ -5394,28 +5394,28 @@
         <v>5.36</v>
       </c>
       <c r="M47">
-        <v>1.149687</v>
+        <v>1.1752356</v>
       </c>
       <c r="N47">
-        <v>4.210313</v>
+        <v>4.184764400000001</v>
       </c>
       <c r="O47">
-        <v>1.05257825</v>
+        <v>1.0461911</v>
       </c>
       <c r="P47">
-        <v>3.15773475</v>
+        <v>3.1385733</v>
       </c>
       <c r="Q47">
-        <v>3.19773475</v>
+        <v>3.1785733</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.08870802578114861</v>
+        <v>0.08937951288257504</v>
       </c>
       <c r="T47">
-        <v>0.8139493935719307</v>
+        <v>0.8266872557561551</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5432,7 +5432,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.662138477690014</v>
+        <v>4.560787641218493</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5440,22 +5440,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06734343695659052</v>
+        <v>0.06811495973354931</v>
       </c>
       <c r="C48">
-        <v>28.6657938485878</v>
+        <v>27.31807809173143</v>
       </c>
       <c r="D48">
-        <v>25.6177938485878</v>
+        <v>24.73207809173143</v>
       </c>
       <c r="E48">
-        <v>10.052</v>
+        <v>10.514</v>
       </c>
       <c r="F48">
-        <v>21.252</v>
+        <v>21.714</v>
       </c>
       <c r="G48">
         <v>24.3</v>
@@ -5476,45 +5476,45 @@
         <v>5.36</v>
       </c>
       <c r="M48">
-        <v>1.1752356</v>
+        <v>1.2550692</v>
       </c>
       <c r="N48">
-        <v>4.184764400000001</v>
+        <v>4.1049308</v>
       </c>
       <c r="O48">
-        <v>1.0461911</v>
+        <v>1.0262327</v>
       </c>
       <c r="P48">
-        <v>3.1385733</v>
+        <v>3.0786981</v>
       </c>
       <c r="Q48">
-        <v>3.1785733</v>
+        <v>3.1186981</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.08937951288257504</v>
+        <v>0.09007633911990434</v>
       </c>
       <c r="T48">
-        <v>0.8266872557561551</v>
+        <v>0.8399057919850671</v>
       </c>
       <c r="U48">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V48">
         <v>0.25</v>
       </c>
       <c r="W48">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>4.560787641218493</v>
+        <v>4.270680851701245</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5522,22 +5522,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06811495973354931</v>
+        <v>0.06802398251050809</v>
       </c>
       <c r="C49">
-        <v>27.31807809173143</v>
+        <v>26.95732258217144</v>
       </c>
       <c r="D49">
-        <v>24.73207809173143</v>
+        <v>24.83332258217144</v>
       </c>
       <c r="E49">
-        <v>10.514</v>
+        <v>10.976</v>
       </c>
       <c r="F49">
-        <v>21.714</v>
+        <v>22.176</v>
       </c>
       <c r="G49">
         <v>24.3</v>
@@ -5558,28 +5558,28 @@
         <v>5.36</v>
       </c>
       <c r="M49">
-        <v>1.2550692</v>
+        <v>1.2817728</v>
       </c>
       <c r="N49">
-        <v>4.1049308</v>
+        <v>4.078227200000001</v>
       </c>
       <c r="O49">
-        <v>1.0262327</v>
+        <v>1.0195568</v>
       </c>
       <c r="P49">
-        <v>3.0786981</v>
+        <v>3.0586704</v>
       </c>
       <c r="Q49">
-        <v>3.1186981</v>
+        <v>3.0986704</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09007633911990434</v>
+        <v>0.0907999663663617</v>
       </c>
       <c r="T49">
-        <v>0.8399057919850671</v>
+        <v>0.8536327334535526</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5596,7 +5596,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.270680851701245</v>
+        <v>4.181708333957468</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5604,22 +5604,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06802398251050809</v>
+        <v>0.06793300528746687</v>
       </c>
       <c r="C50">
-        <v>26.95732258217144</v>
+        <v>26.59739939903698</v>
       </c>
       <c r="D50">
-        <v>24.83332258217144</v>
+        <v>24.93539939903698</v>
       </c>
       <c r="E50">
-        <v>10.976</v>
+        <v>11.438</v>
       </c>
       <c r="F50">
-        <v>22.176</v>
+        <v>22.638</v>
       </c>
       <c r="G50">
         <v>24.3</v>
@@ -5640,28 +5640,28 @@
         <v>5.36</v>
       </c>
       <c r="M50">
-        <v>1.2817728</v>
+        <v>1.3084764</v>
       </c>
       <c r="N50">
-        <v>4.078227200000001</v>
+        <v>4.0515236</v>
       </c>
       <c r="O50">
-        <v>1.0195568</v>
+        <v>1.0128809</v>
       </c>
       <c r="P50">
-        <v>3.0586704</v>
+        <v>3.0386427</v>
       </c>
       <c r="Q50">
-        <v>3.0986704</v>
+        <v>3.078642700000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.0907999663663617</v>
+        <v>0.09155197115189583</v>
       </c>
       <c r="T50">
-        <v>0.8536327334535526</v>
+        <v>0.8678979863521747</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -5678,7 +5678,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.181708333957468</v>
+        <v>4.096367347550173</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5686,22 +5686,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06793300528746687</v>
+        <v>0.06784202806442566</v>
       </c>
       <c r="C51">
-        <v>26.59739939903698</v>
+        <v>26.23831884846864</v>
       </c>
       <c r="D51">
-        <v>24.93539939903698</v>
+        <v>25.03831884846864</v>
       </c>
       <c r="E51">
-        <v>11.438</v>
+        <v>11.9</v>
       </c>
       <c r="F51">
-        <v>22.638</v>
+        <v>23.1</v>
       </c>
       <c r="G51">
         <v>24.3</v>
@@ -5722,28 +5722,28 @@
         <v>5.36</v>
       </c>
       <c r="M51">
-        <v>1.3084764</v>
+        <v>1.33518</v>
       </c>
       <c r="N51">
-        <v>4.0515236</v>
+        <v>4.02482</v>
       </c>
       <c r="O51">
-        <v>1.0128809</v>
+        <v>1.006205</v>
       </c>
       <c r="P51">
-        <v>3.0386427</v>
+        <v>3.018615</v>
       </c>
       <c r="Q51">
-        <v>3.078642700000001</v>
+        <v>3.058615</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09155197115189583</v>
+        <v>0.09233405612885132</v>
       </c>
       <c r="T51">
-        <v>0.8678979863521747</v>
+        <v>0.8827338493667419</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.096367347550173</v>
+        <v>4.014440000599169</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5768,22 +5768,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06784202806442566</v>
+        <v>0.06908980084138444</v>
       </c>
       <c r="C52">
-        <v>26.23831884846864</v>
+        <v>24.4348675903532</v>
       </c>
       <c r="D52">
-        <v>25.03831884846864</v>
+        <v>23.6968675903532</v>
       </c>
       <c r="E52">
-        <v>11.9</v>
+        <v>12.362</v>
       </c>
       <c r="F52">
-        <v>23.1</v>
+        <v>23.562</v>
       </c>
       <c r="G52">
         <v>24.3</v>
@@ -5804,45 +5804,45 @@
         <v>5.36</v>
       </c>
       <c r="M52">
-        <v>1.33518</v>
+        <v>1.4443506</v>
       </c>
       <c r="N52">
-        <v>4.02482</v>
+        <v>3.9156494</v>
       </c>
       <c r="O52">
-        <v>1.006205</v>
+        <v>0.9789123500000001</v>
       </c>
       <c r="P52">
-        <v>3.018615</v>
+        <v>2.936737050000001</v>
       </c>
       <c r="Q52">
-        <v>3.058615</v>
+        <v>2.976737050000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09233405612885132</v>
+        <v>0.0931480629416009</v>
       </c>
       <c r="T52">
-        <v>0.8827338493667419</v>
+        <v>0.898175257810475</v>
       </c>
       <c r="U52">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V52">
         <v>0.25</v>
       </c>
       <c r="W52">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y52">
-        <v>4.014440000599169</v>
+        <v>3.711010332255894</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5850,22 +5850,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06908980084138444</v>
+        <v>0.06902507361834322</v>
       </c>
       <c r="C53">
-        <v>24.4348675903532</v>
+        <v>24.03890968171983</v>
       </c>
       <c r="D53">
-        <v>23.6968675903532</v>
+        <v>23.76290968171983</v>
       </c>
       <c r="E53">
-        <v>12.362</v>
+        <v>12.824</v>
       </c>
       <c r="F53">
-        <v>23.562</v>
+        <v>24.024</v>
       </c>
       <c r="G53">
         <v>24.3</v>
@@ -5886,28 +5886,28 @@
         <v>5.36</v>
       </c>
       <c r="M53">
-        <v>1.4443506</v>
+        <v>1.4726712</v>
       </c>
       <c r="N53">
-        <v>3.9156494</v>
+        <v>3.887328800000001</v>
       </c>
       <c r="O53">
-        <v>0.9789123500000001</v>
+        <v>0.9718322000000001</v>
       </c>
       <c r="P53">
-        <v>2.936737050000001</v>
+        <v>2.9154966</v>
       </c>
       <c r="Q53">
-        <v>2.976737050000001</v>
+        <v>2.9554966</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.0931480629416009</v>
+        <v>0.09399598670488171</v>
       </c>
       <c r="T53">
-        <v>0.898175257810475</v>
+        <v>0.914260058272697</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5924,7 +5924,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.711010332255894</v>
+        <v>3.639644748943281</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5932,22 +5932,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06902507361834322</v>
+        <v>0.06896034639530201</v>
       </c>
       <c r="C54">
-        <v>24.03890968171983</v>
+        <v>23.64332091447189</v>
       </c>
       <c r="D54">
-        <v>23.76290968171983</v>
+        <v>23.82932091447189</v>
       </c>
       <c r="E54">
-        <v>12.824</v>
+        <v>13.286</v>
       </c>
       <c r="F54">
-        <v>24.024</v>
+        <v>24.486</v>
       </c>
       <c r="G54">
         <v>24.3</v>
@@ -5968,28 +5968,28 @@
         <v>5.36</v>
       </c>
       <c r="M54">
-        <v>1.4726712</v>
+        <v>1.5009918</v>
       </c>
       <c r="N54">
-        <v>3.887328800000001</v>
+        <v>3.8590082</v>
       </c>
       <c r="O54">
-        <v>0.9718322000000001</v>
+        <v>0.96475205</v>
       </c>
       <c r="P54">
-        <v>2.9154966</v>
+        <v>2.89425615</v>
       </c>
       <c r="Q54">
-        <v>2.9554966</v>
+        <v>2.93425615</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09399598670488171</v>
+        <v>0.0948799923304298</v>
       </c>
       <c r="T54">
-        <v>0.914260058272697</v>
+        <v>0.9310293183290561</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.639644748943281</v>
+        <v>3.570972206510388</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6014,22 +6014,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06896034639530201</v>
+        <v>0.06889561917226079</v>
       </c>
       <c r="C55">
-        <v>23.64332091447189</v>
+        <v>23.24810439224953</v>
       </c>
       <c r="D55">
-        <v>23.82932091447189</v>
+        <v>23.89610439224954</v>
       </c>
       <c r="E55">
-        <v>13.286</v>
+        <v>13.748</v>
       </c>
       <c r="F55">
-        <v>24.486</v>
+        <v>24.948</v>
       </c>
       <c r="G55">
         <v>24.3</v>
@@ -6050,28 +6050,28 @@
         <v>5.36</v>
       </c>
       <c r="M55">
-        <v>1.5009918</v>
+        <v>1.5293124</v>
       </c>
       <c r="N55">
-        <v>3.8590082</v>
+        <v>3.8306876</v>
       </c>
       <c r="O55">
-        <v>0.96475205</v>
+        <v>0.9576719</v>
       </c>
       <c r="P55">
-        <v>2.89425615</v>
+        <v>2.8730157</v>
       </c>
       <c r="Q55">
-        <v>2.93425615</v>
+        <v>2.9130157</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.0948799923304298</v>
+        <v>0.09580243298317564</v>
       </c>
       <c r="T55">
-        <v>0.9310293183290561</v>
+        <v>0.9485276766487352</v>
       </c>
       <c r="U55">
         <v>0.0613</v>
@@ -6088,7 +6088,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.570972206510388</v>
+        <v>3.504843091575011</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6096,22 +6096,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06889561917226079</v>
+        <v>0.06998589194921959</v>
       </c>
       <c r="C56">
-        <v>23.24810439224953</v>
+        <v>21.70889491207257</v>
       </c>
       <c r="D56">
-        <v>23.89610439224954</v>
+        <v>22.81889491207257</v>
       </c>
       <c r="E56">
-        <v>13.748</v>
+        <v>14.21</v>
       </c>
       <c r="F56">
-        <v>24.948</v>
+        <v>25.41</v>
       </c>
       <c r="G56">
         <v>24.3</v>
@@ -6132,45 +6132,45 @@
         <v>5.36</v>
       </c>
       <c r="M56">
-        <v>1.5293124</v>
+        <v>1.628781</v>
       </c>
       <c r="N56">
-        <v>3.8306876</v>
+        <v>3.731219</v>
       </c>
       <c r="O56">
-        <v>0.9576719</v>
+        <v>0.9328047500000001</v>
       </c>
       <c r="P56">
-        <v>2.8730157</v>
+        <v>2.79841425</v>
       </c>
       <c r="Q56">
-        <v>2.9130157</v>
+        <v>2.83841425</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09580243298317564</v>
+        <v>0.09676587099826572</v>
       </c>
       <c r="T56">
-        <v>0.9485276766487352</v>
+        <v>0.9668037397826222</v>
       </c>
       <c r="U56">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y56">
-        <v>3.504843091575011</v>
+        <v>3.290804595584059</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6178,22 +6178,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06998589194921959</v>
+        <v>0.06994216472617837</v>
       </c>
       <c r="C57">
-        <v>21.70889491207257</v>
+        <v>21.28822537761662</v>
       </c>
       <c r="D57">
-        <v>22.81889491207257</v>
+        <v>22.86022537761663</v>
       </c>
       <c r="E57">
-        <v>14.21</v>
+        <v>14.672</v>
       </c>
       <c r="F57">
-        <v>25.41</v>
+        <v>25.872</v>
       </c>
       <c r="G57">
         <v>24.3</v>
@@ -6214,28 +6214,28 @@
         <v>5.36</v>
       </c>
       <c r="M57">
-        <v>1.628781</v>
+        <v>1.6583952</v>
       </c>
       <c r="N57">
-        <v>3.731219</v>
+        <v>3.7016048</v>
       </c>
       <c r="O57">
-        <v>0.9328047500000001</v>
+        <v>0.9254012</v>
       </c>
       <c r="P57">
-        <v>2.79841425</v>
+        <v>2.7762036</v>
       </c>
       <c r="Q57">
-        <v>2.83841425</v>
+        <v>2.8162036</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09676587099826572</v>
+        <v>0.09777310165040537</v>
       </c>
       <c r="T57">
-        <v>0.9668037397826222</v>
+        <v>0.9859105330589585</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -6252,7 +6252,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.290804595584059</v>
+        <v>3.232040227805772</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6260,22 +6260,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06994216472617837</v>
+        <v>0.06989843750313714</v>
       </c>
       <c r="C58">
-        <v>21.28822537761662</v>
+        <v>20.86770583350634</v>
       </c>
       <c r="D58">
-        <v>22.86022537761663</v>
+        <v>22.90170583350634</v>
       </c>
       <c r="E58">
-        <v>14.672</v>
+        <v>15.134</v>
       </c>
       <c r="F58">
-        <v>25.872</v>
+        <v>26.334</v>
       </c>
       <c r="G58">
         <v>24.3</v>
@@ -6296,28 +6296,28 @@
         <v>5.36</v>
       </c>
       <c r="M58">
-        <v>1.6583952</v>
+        <v>1.6880094</v>
       </c>
       <c r="N58">
-        <v>3.7016048</v>
+        <v>3.6719906</v>
       </c>
       <c r="O58">
-        <v>0.9254012</v>
+        <v>0.91799765</v>
       </c>
       <c r="P58">
-        <v>2.7762036</v>
+        <v>2.75399295</v>
       </c>
       <c r="Q58">
-        <v>2.8162036</v>
+        <v>2.79399295</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09777310165040537</v>
+        <v>0.09882718023985382</v>
       </c>
       <c r="T58">
-        <v>0.9859105330589585</v>
+        <v>1.005906014394659</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.232040227805772</v>
+        <v>3.175337767668829</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6342,22 +6342,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06989843750313714</v>
+        <v>0.06985471028009593</v>
       </c>
       <c r="C59">
-        <v>20.86770583350634</v>
+        <v>20.44733709770969</v>
       </c>
       <c r="D59">
-        <v>22.90170583350634</v>
+        <v>22.94333709770969</v>
       </c>
       <c r="E59">
-        <v>15.134</v>
+        <v>15.59600000000001</v>
       </c>
       <c r="F59">
-        <v>26.334</v>
+        <v>26.79600000000001</v>
       </c>
       <c r="G59">
         <v>24.3</v>
@@ -6378,28 +6378,28 @@
         <v>5.36</v>
       </c>
       <c r="M59">
-        <v>1.6880094</v>
+        <v>1.7176236</v>
       </c>
       <c r="N59">
-        <v>3.6719906</v>
+        <v>3.6423764</v>
       </c>
       <c r="O59">
-        <v>0.91799765</v>
+        <v>0.9105941</v>
       </c>
       <c r="P59">
-        <v>2.75399295</v>
+        <v>2.7317823</v>
       </c>
       <c r="Q59">
-        <v>2.79399295</v>
+        <v>2.7717823</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.09882718023985382</v>
+        <v>0.09993145304784745</v>
       </c>
       <c r="T59">
-        <v>1.005906014394659</v>
+        <v>1.026853661508251</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6416,7 +6416,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.175337767668829</v>
+        <v>3.120590564777987</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6424,22 +6424,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06985471028009593</v>
+        <v>0.06981098305705472</v>
       </c>
       <c r="C60">
-        <v>20.4473370977097</v>
+        <v>20.02711999415328</v>
       </c>
       <c r="D60">
-        <v>22.94333709770969</v>
+        <v>22.98511999415327</v>
       </c>
       <c r="E60">
-        <v>15.596</v>
+        <v>16.058</v>
       </c>
       <c r="F60">
-        <v>26.796</v>
+        <v>27.258</v>
       </c>
       <c r="G60">
         <v>24.3</v>
@@ -6460,28 +6460,28 @@
         <v>5.36</v>
       </c>
       <c r="M60">
-        <v>1.7176236</v>
+        <v>1.7472378</v>
       </c>
       <c r="N60">
-        <v>3.6423764</v>
+        <v>3.612762200000001</v>
       </c>
       <c r="O60">
-        <v>0.9105941000000001</v>
+        <v>0.9031905500000001</v>
       </c>
       <c r="P60">
-        <v>2.7317823</v>
+        <v>2.70957165</v>
       </c>
       <c r="Q60">
-        <v>2.7717823</v>
+        <v>2.74957165</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.09993145304784744</v>
+        <v>0.1010895928220847</v>
       </c>
       <c r="T60">
-        <v>1.026853661508251</v>
+        <v>1.048823145066408</v>
       </c>
       <c r="U60">
         <v>0.0641</v>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.120590564777987</v>
+        <v>3.067699199273276</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6506,22 +6506,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06981098305705472</v>
+        <v>0.0697672558340135</v>
       </c>
       <c r="C61">
-        <v>20.02711999415328</v>
+        <v>19.60705535277648</v>
       </c>
       <c r="D61">
-        <v>22.98511999415327</v>
+        <v>23.02705535277648</v>
       </c>
       <c r="E61">
-        <v>16.058</v>
+        <v>16.52</v>
       </c>
       <c r="F61">
-        <v>27.258</v>
+        <v>27.72</v>
       </c>
       <c r="G61">
         <v>24.3</v>
@@ -6542,28 +6542,28 @@
         <v>5.36</v>
       </c>
       <c r="M61">
-        <v>1.7472378</v>
+        <v>1.776852</v>
       </c>
       <c r="N61">
-        <v>3.612762200000001</v>
+        <v>3.583148</v>
       </c>
       <c r="O61">
-        <v>0.9031905500000001</v>
+        <v>0.895787</v>
       </c>
       <c r="P61">
-        <v>2.70957165</v>
+        <v>2.687361</v>
       </c>
       <c r="Q61">
-        <v>2.74957165</v>
+        <v>2.727361</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1010895928220847</v>
+        <v>0.1023056395850337</v>
       </c>
       <c r="T61">
-        <v>1.048823145066408</v>
+        <v>1.071891102802472</v>
       </c>
       <c r="U61">
         <v>0.0641</v>
@@ -6580,7 +6580,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>3.067699199273276</v>
+        <v>3.016570879285387</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6588,22 +6588,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.0697672558340135</v>
+        <v>0.07329202861097228</v>
       </c>
       <c r="C62">
-        <v>19.60705535277648</v>
+        <v>16.1927400111361</v>
       </c>
       <c r="D62">
-        <v>23.02705535277648</v>
+        <v>20.0747400111361</v>
       </c>
       <c r="E62">
-        <v>16.52</v>
+        <v>16.982</v>
       </c>
       <c r="F62">
-        <v>27.72</v>
+        <v>28.182</v>
       </c>
       <c r="G62">
         <v>24.3</v>
@@ -6624,45 +6624,45 @@
         <v>5.36</v>
       </c>
       <c r="M62">
-        <v>1.776852</v>
+        <v>2.0262858</v>
       </c>
       <c r="N62">
-        <v>3.583148</v>
+        <v>3.3337142</v>
       </c>
       <c r="O62">
-        <v>0.895787</v>
+        <v>0.83342855</v>
       </c>
       <c r="P62">
-        <v>2.687361</v>
+        <v>2.50028565</v>
       </c>
       <c r="Q62">
-        <v>2.727361</v>
+        <v>2.54028565</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1023056395850337</v>
+        <v>0.1035840477204417</v>
       </c>
       <c r="T62">
-        <v>1.071891102802472</v>
+        <v>1.09614203273013</v>
       </c>
       <c r="U62">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V62">
         <v>0.25</v>
       </c>
       <c r="W62">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>3.016570879285387</v>
+        <v>2.645233954657334</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6670,22 +6670,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07329202861097228</v>
+        <v>0.07330680138793105</v>
       </c>
       <c r="C63">
-        <v>16.1927400111361</v>
+        <v>15.7199586900909</v>
       </c>
       <c r="D63">
-        <v>20.0747400111361</v>
+        <v>20.0639586900909</v>
       </c>
       <c r="E63">
-        <v>16.982</v>
+        <v>17.444</v>
       </c>
       <c r="F63">
-        <v>28.182</v>
+        <v>28.644</v>
       </c>
       <c r="G63">
         <v>24.3</v>
@@ -6706,28 +6706,28 @@
         <v>5.36</v>
       </c>
       <c r="M63">
-        <v>2.0262858</v>
+        <v>2.0595036</v>
       </c>
       <c r="N63">
-        <v>3.3337142</v>
+        <v>3.3004964</v>
       </c>
       <c r="O63">
-        <v>0.83342855</v>
+        <v>0.8251241</v>
       </c>
       <c r="P63">
-        <v>2.50028565</v>
+        <v>2.4753723</v>
       </c>
       <c r="Q63">
-        <v>2.54028565</v>
+        <v>2.5153723</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1035840477204417</v>
+        <v>0.1049297404945554</v>
       </c>
       <c r="T63">
-        <v>1.09614203273013</v>
+        <v>1.121669327390822</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6744,7 +6744,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.645233954657334</v>
+        <v>2.602568890872538</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6752,22 +6752,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07330680138793105</v>
+        <v>0.07332157416488985</v>
       </c>
       <c r="C64">
-        <v>15.7199586900909</v>
+        <v>15.24718894324199</v>
       </c>
       <c r="D64">
-        <v>20.0639586900909</v>
+        <v>20.053188943242</v>
       </c>
       <c r="E64">
-        <v>17.444</v>
+        <v>17.906</v>
       </c>
       <c r="F64">
-        <v>28.644</v>
+        <v>29.106</v>
       </c>
       <c r="G64">
         <v>24.3</v>
@@ -6788,28 +6788,28 @@
         <v>5.36</v>
       </c>
       <c r="M64">
-        <v>2.0595036</v>
+        <v>2.0927214</v>
       </c>
       <c r="N64">
-        <v>3.3004964</v>
+        <v>3.2672786</v>
       </c>
       <c r="O64">
-        <v>0.8251241</v>
+        <v>0.81681965</v>
       </c>
       <c r="P64">
-        <v>2.4753723</v>
+        <v>2.45045895</v>
       </c>
       <c r="Q64">
-        <v>2.5153723</v>
+        <v>2.49045895</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1049297404945554</v>
+        <v>0.1063481734186212</v>
       </c>
       <c r="T64">
-        <v>1.121669327390822</v>
+        <v>1.148576475816958</v>
       </c>
       <c r="U64">
         <v>0.07190000000000001</v>
@@ -6826,7 +6826,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.602568890872538</v>
+        <v>2.561258273557101</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6834,22 +6834,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07332157416488985</v>
+        <v>0.07333634694184862</v>
       </c>
       <c r="C65">
-        <v>15.24718894324199</v>
+        <v>14.77443075196135</v>
       </c>
       <c r="D65">
-        <v>20.053188943242</v>
+        <v>20.04243075196135</v>
       </c>
       <c r="E65">
-        <v>17.906</v>
+        <v>18.368</v>
       </c>
       <c r="F65">
-        <v>29.106</v>
+        <v>29.568</v>
       </c>
       <c r="G65">
         <v>24.3</v>
@@ -6870,28 +6870,28 @@
         <v>5.36</v>
       </c>
       <c r="M65">
-        <v>2.0927214</v>
+        <v>2.1259392</v>
       </c>
       <c r="N65">
-        <v>3.2672786</v>
+        <v>3.2340608</v>
       </c>
       <c r="O65">
-        <v>0.81681965</v>
+        <v>0.8085152</v>
       </c>
       <c r="P65">
-        <v>2.45045895</v>
+        <v>2.4255456</v>
       </c>
       <c r="Q65">
-        <v>2.49045895</v>
+        <v>2.4655456</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1063481734186212</v>
+        <v>0.1078454081718017</v>
       </c>
       <c r="T65">
-        <v>1.148576475816958</v>
+        <v>1.176978465822323</v>
       </c>
       <c r="U65">
         <v>0.07190000000000001</v>
@@ -6908,7 +6908,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.561258273557101</v>
+        <v>2.521238613032772</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6916,22 +6916,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07333634694184862</v>
+        <v>0.07525236971880742</v>
       </c>
       <c r="C66">
-        <v>14.77443075196135</v>
+        <v>13.00857119183044</v>
       </c>
       <c r="D66">
-        <v>20.04243075196135</v>
+        <v>18.73857119183044</v>
       </c>
       <c r="E66">
-        <v>18.368</v>
+        <v>18.83</v>
       </c>
       <c r="F66">
-        <v>29.568</v>
+        <v>30.03</v>
       </c>
       <c r="G66">
         <v>24.3</v>
@@ -6952,45 +6952,45 @@
         <v>5.36</v>
       </c>
       <c r="M66">
-        <v>2.1259392</v>
+        <v>2.276274</v>
       </c>
       <c r="N66">
-        <v>3.2340608</v>
+        <v>3.083726</v>
       </c>
       <c r="O66">
-        <v>0.8085152</v>
+        <v>0.7709315</v>
       </c>
       <c r="P66">
-        <v>2.4255456</v>
+        <v>2.3127945</v>
       </c>
       <c r="Q66">
-        <v>2.4655456</v>
+        <v>2.3527945</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1078454081718017</v>
+        <v>0.1094281991965926</v>
       </c>
       <c r="T66">
-        <v>1.176978465822323</v>
+        <v>1.207003426685137</v>
       </c>
       <c r="U66">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V66">
         <v>0.25</v>
       </c>
       <c r="W66">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y66">
-        <v>2.521238613032772</v>
+        <v>2.354725309870428</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6998,22 +6998,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07525236971880742</v>
+        <v>0.0752963924957662</v>
       </c>
       <c r="C67">
-        <v>13.00857119183044</v>
+        <v>12.51860424840768</v>
       </c>
       <c r="D67">
-        <v>18.73857119183044</v>
+        <v>18.71060424840769</v>
       </c>
       <c r="E67">
-        <v>18.83</v>
+        <v>19.29200000000001</v>
       </c>
       <c r="F67">
-        <v>30.03</v>
+        <v>30.492</v>
       </c>
       <c r="G67">
         <v>24.3</v>
@@ -7034,28 +7034,28 @@
         <v>5.36</v>
       </c>
       <c r="M67">
-        <v>2.276274</v>
+        <v>2.3112936</v>
       </c>
       <c r="N67">
-        <v>3.083726</v>
+        <v>3.0487064</v>
       </c>
       <c r="O67">
-        <v>0.7709315</v>
+        <v>0.7621766</v>
       </c>
       <c r="P67">
-        <v>2.3127945</v>
+        <v>2.2865298</v>
       </c>
       <c r="Q67">
-        <v>2.3527945</v>
+        <v>2.3265298</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1094281991965926</v>
+        <v>0.1111040955757829</v>
       </c>
       <c r="T67">
-        <v>1.207003426685137</v>
+        <v>1.238794561716352</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -7072,7 +7072,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.354725309870428</v>
+        <v>2.31904765366027</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7080,22 +7080,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0752963924957662</v>
+        <v>0.07534041527272498</v>
       </c>
       <c r="C68">
-        <v>12.51860424840768</v>
+        <v>12.02872066078757</v>
       </c>
       <c r="D68">
-        <v>18.71060424840769</v>
+        <v>18.68272066078758</v>
       </c>
       <c r="E68">
-        <v>19.29200000000001</v>
+        <v>19.754</v>
       </c>
       <c r="F68">
-        <v>30.492</v>
+        <v>30.954</v>
       </c>
       <c r="G68">
         <v>24.3</v>
@@ -7116,28 +7116,28 @@
         <v>5.36</v>
       </c>
       <c r="M68">
-        <v>2.3112936</v>
+        <v>2.3463132</v>
       </c>
       <c r="N68">
-        <v>3.0487064</v>
+        <v>3.0136868</v>
       </c>
       <c r="O68">
-        <v>0.7621766</v>
+        <v>0.7534217</v>
       </c>
       <c r="P68">
-        <v>2.2865298</v>
+        <v>2.2602651</v>
       </c>
       <c r="Q68">
-        <v>2.3265298</v>
+        <v>2.3002651</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1111040955757829</v>
+        <v>0.1128815614324999</v>
       </c>
       <c r="T68">
-        <v>1.238794561716352</v>
+        <v>1.272512432204005</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -7154,7 +7154,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.31904765366027</v>
+        <v>2.284435002113102</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7162,22 +7162,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07534041527272498</v>
+        <v>0.07538443804968377</v>
       </c>
       <c r="C69">
-        <v>12.02872066078757</v>
+        <v>11.5389200568602</v>
       </c>
       <c r="D69">
-        <v>18.68272066078758</v>
+        <v>18.6549200568602</v>
       </c>
       <c r="E69">
-        <v>19.754</v>
+        <v>20.216</v>
       </c>
       <c r="F69">
-        <v>30.954</v>
+        <v>31.416</v>
       </c>
       <c r="G69">
         <v>24.3</v>
@@ -7198,28 +7198,28 @@
         <v>5.36</v>
       </c>
       <c r="M69">
-        <v>2.3463132</v>
+        <v>2.3813328</v>
       </c>
       <c r="N69">
-        <v>3.0136868</v>
+        <v>2.9786672</v>
       </c>
       <c r="O69">
-        <v>0.7534217</v>
+        <v>0.7446668</v>
       </c>
       <c r="P69">
-        <v>2.2602651</v>
+        <v>2.2340004</v>
       </c>
       <c r="Q69">
-        <v>2.3002651</v>
+        <v>2.2740004</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1128815614324999</v>
+        <v>0.1147701189052618</v>
       </c>
       <c r="T69">
-        <v>1.272512432204005</v>
+        <v>1.308337669597136</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.284435002113102</v>
+        <v>2.250840369729086</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7244,22 +7244,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07538443804968377</v>
+        <v>0.07542846082664255</v>
       </c>
       <c r="C70">
-        <v>11.5389200568602</v>
+        <v>11.04920206672726</v>
       </c>
       <c r="D70">
-        <v>18.6549200568602</v>
+        <v>18.62720206672726</v>
       </c>
       <c r="E70">
-        <v>20.216</v>
+        <v>20.678</v>
       </c>
       <c r="F70">
-        <v>31.416</v>
+        <v>31.878</v>
       </c>
       <c r="G70">
         <v>24.3</v>
@@ -7280,28 +7280,28 @@
         <v>5.36</v>
       </c>
       <c r="M70">
-        <v>2.3813328</v>
+        <v>2.416352400000001</v>
       </c>
       <c r="N70">
-        <v>2.9786672</v>
+        <v>2.9436476</v>
       </c>
       <c r="O70">
-        <v>0.7446668</v>
+        <v>0.7359119</v>
       </c>
       <c r="P70">
-        <v>2.2340004</v>
+        <v>2.2077357</v>
       </c>
       <c r="Q70">
-        <v>2.2740004</v>
+        <v>2.2477357</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1147701189052618</v>
+        <v>0.1167805187956211</v>
       </c>
       <c r="T70">
-        <v>1.308337669597136</v>
+        <v>1.346474212628533</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.250840369729086</v>
+        <v>2.218219494805476</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7326,22 +7326,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07542846082664255</v>
+        <v>0.07547248360360134</v>
       </c>
       <c r="C71">
-        <v>11.04920206672726</v>
+        <v>10.55956632268558</v>
       </c>
       <c r="D71">
-        <v>18.62720206672726</v>
+        <v>18.59956632268559</v>
       </c>
       <c r="E71">
-        <v>20.678</v>
+        <v>21.14</v>
       </c>
       <c r="F71">
-        <v>31.878</v>
+        <v>32.34</v>
       </c>
       <c r="G71">
         <v>24.3</v>
@@ -7362,28 +7362,28 @@
         <v>5.36</v>
       </c>
       <c r="M71">
-        <v>2.416352400000001</v>
+        <v>2.451372000000001</v>
       </c>
       <c r="N71">
-        <v>2.9436476</v>
+        <v>2.908628</v>
       </c>
       <c r="O71">
-        <v>0.7359119</v>
+        <v>0.7271569999999999</v>
       </c>
       <c r="P71">
-        <v>2.2077357</v>
+        <v>2.181471</v>
       </c>
       <c r="Q71">
-        <v>2.2477357</v>
+        <v>2.221471</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1167805187956211</v>
+        <v>0.1189249453453378</v>
       </c>
       <c r="T71">
-        <v>1.346474212628533</v>
+        <v>1.387153191862023</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.218219494805476</v>
+        <v>2.186530644879683</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7408,22 +7408,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07547248360360134</v>
+        <v>0.07551650638056012</v>
       </c>
       <c r="C72">
-        <v>10.55956632268558</v>
+        <v>10.07001245921093</v>
       </c>
       <c r="D72">
-        <v>18.59956632268559</v>
+        <v>18.57201245921093</v>
       </c>
       <c r="E72">
-        <v>21.14</v>
+        <v>21.60200000000001</v>
       </c>
       <c r="F72">
-        <v>32.34</v>
+        <v>32.80200000000001</v>
       </c>
       <c r="G72">
         <v>24.3</v>
@@ -7444,28 +7444,28 @@
         <v>5.36</v>
       </c>
       <c r="M72">
-        <v>2.451372000000001</v>
+        <v>2.486391600000001</v>
       </c>
       <c r="N72">
-        <v>2.908628</v>
+        <v>2.8736084</v>
       </c>
       <c r="O72">
-        <v>0.7271569999999999</v>
+        <v>0.7184020999999999</v>
       </c>
       <c r="P72">
-        <v>2.181471</v>
+        <v>2.1552063</v>
       </c>
       <c r="Q72">
-        <v>2.221471</v>
+        <v>2.1952063</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1189249453453378</v>
+        <v>0.1212172633812418</v>
       </c>
       <c r="T72">
-        <v>1.387153191862023</v>
+        <v>1.430637617939203</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7482,7 +7482,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.186530644879683</v>
+        <v>2.155734438613772</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7490,22 +7490,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07551650638056012</v>
+        <v>0.0755605291575189</v>
       </c>
       <c r="C73">
-        <v>10.07001245921094</v>
+        <v>9.580540112941812</v>
       </c>
       <c r="D73">
-        <v>18.57201245921093</v>
+        <v>18.54454011294181</v>
       </c>
       <c r="E73">
-        <v>21.602</v>
+        <v>22.064</v>
       </c>
       <c r="F73">
-        <v>32.802</v>
+        <v>33.264</v>
       </c>
       <c r="G73">
         <v>24.3</v>
@@ -7526,28 +7526,28 @@
         <v>5.36</v>
       </c>
       <c r="M73">
-        <v>2.4863916</v>
+        <v>2.521411200000001</v>
       </c>
       <c r="N73">
-        <v>2.8736084</v>
+        <v>2.8385888</v>
       </c>
       <c r="O73">
-        <v>0.7184021</v>
+        <v>0.7096471999999999</v>
       </c>
       <c r="P73">
-        <v>2.1552063</v>
+        <v>2.1289416</v>
       </c>
       <c r="Q73">
-        <v>2.1952063</v>
+        <v>2.1689416</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1212172633812418</v>
+        <v>0.1236733184197104</v>
       </c>
       <c r="T73">
-        <v>1.430637617939202</v>
+        <v>1.477228074450466</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7564,7 +7564,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.155734438613773</v>
+        <v>2.125793682521914</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7572,22 +7572,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0755605291575189</v>
+        <v>0.07560455193447768</v>
       </c>
       <c r="C74">
-        <v>9.580540112941812</v>
+        <v>9.091148922663564</v>
       </c>
       <c r="D74">
-        <v>18.54454011294181</v>
+        <v>18.51714892266357</v>
       </c>
       <c r="E74">
-        <v>22.064</v>
+        <v>22.526</v>
       </c>
       <c r="F74">
-        <v>33.264</v>
+        <v>33.726</v>
       </c>
       <c r="G74">
         <v>24.3</v>
@@ -7608,28 +7608,28 @@
         <v>5.36</v>
       </c>
       <c r="M74">
-        <v>2.521411200000001</v>
+        <v>2.5564308</v>
       </c>
       <c r="N74">
-        <v>2.8385888</v>
+        <v>2.8035692</v>
       </c>
       <c r="O74">
-        <v>0.7096471999999999</v>
+        <v>0.7008923</v>
       </c>
       <c r="P74">
-        <v>2.1289416</v>
+        <v>2.1026769</v>
       </c>
       <c r="Q74">
-        <v>2.1689416</v>
+        <v>2.1426769</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1236733184197104</v>
+        <v>0.1263113034610285</v>
       </c>
       <c r="T74">
-        <v>1.477228074450466</v>
+        <v>1.52726967588849</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7646,7 +7646,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.125793682521914</v>
+        <v>2.096673221117505</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7654,22 +7654,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07560455193447768</v>
+        <v>0.07564857471143646</v>
       </c>
       <c r="C75">
-        <v>9.091148922663564</v>
+        <v>8.6018385292925</v>
       </c>
       <c r="D75">
-        <v>18.51714892266357</v>
+        <v>18.4898385292925</v>
       </c>
       <c r="E75">
-        <v>22.526</v>
+        <v>22.988</v>
       </c>
       <c r="F75">
-        <v>33.726</v>
+        <v>34.188</v>
       </c>
       <c r="G75">
         <v>24.3</v>
@@ -7690,28 +7690,28 @@
         <v>5.36</v>
       </c>
       <c r="M75">
-        <v>2.5564308</v>
+        <v>2.5914504</v>
       </c>
       <c r="N75">
-        <v>2.8035692</v>
+        <v>2.7685496</v>
       </c>
       <c r="O75">
-        <v>0.7008923</v>
+        <v>0.6921374</v>
       </c>
       <c r="P75">
-        <v>2.1026769</v>
+        <v>2.0764122</v>
       </c>
       <c r="Q75">
-        <v>2.1426769</v>
+        <v>2.1164122</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1263113034610285</v>
+        <v>0.1291522104286018</v>
       </c>
       <c r="T75">
-        <v>1.52726967588849</v>
+        <v>1.581160631283285</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.096673221117505</v>
+        <v>2.068339799210511</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7736,22 +7736,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07564857471143646</v>
+        <v>0.07569259748839526</v>
       </c>
       <c r="C76">
-        <v>8.6018385292925</v>
+        <v>8.112608575860207</v>
       </c>
       <c r="D76">
-        <v>18.4898385292925</v>
+        <v>18.46260857586022</v>
       </c>
       <c r="E76">
-        <v>22.988</v>
+        <v>23.45000000000001</v>
       </c>
       <c r="F76">
-        <v>34.188</v>
+        <v>34.65000000000001</v>
       </c>
       <c r="G76">
         <v>24.3</v>
@@ -7772,28 +7772,28 @@
         <v>5.36</v>
       </c>
       <c r="M76">
-        <v>2.5914504</v>
+        <v>2.626470000000001</v>
       </c>
       <c r="N76">
-        <v>2.7685496</v>
+        <v>2.73353</v>
       </c>
       <c r="O76">
-        <v>0.6921374</v>
+        <v>0.6833824999999999</v>
       </c>
       <c r="P76">
-        <v>2.0764122</v>
+        <v>2.0501475</v>
       </c>
       <c r="Q76">
-        <v>2.1164122</v>
+        <v>2.0901475</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1291522104286018</v>
+        <v>0.132220389953581</v>
       </c>
       <c r="T76">
-        <v>1.581160631283285</v>
+        <v>1.639362863109664</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7810,7 +7810,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.068339799210511</v>
+        <v>2.040761935221038</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7818,22 +7818,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07569259748839526</v>
+        <v>0.07573662026535403</v>
       </c>
       <c r="C77">
-        <v>8.112608575860207</v>
+        <v>7.623458707498052</v>
       </c>
       <c r="D77">
-        <v>18.46260857586022</v>
+        <v>18.43545870749805</v>
       </c>
       <c r="E77">
-        <v>23.45000000000001</v>
+        <v>23.912</v>
       </c>
       <c r="F77">
-        <v>34.65000000000001</v>
+        <v>35.112</v>
       </c>
       <c r="G77">
         <v>24.3</v>
@@ -7854,28 +7854,28 @@
         <v>5.36</v>
       </c>
       <c r="M77">
-        <v>2.626470000000001</v>
+        <v>2.6614896</v>
       </c>
       <c r="N77">
-        <v>2.73353</v>
+        <v>2.6985104</v>
       </c>
       <c r="O77">
-        <v>0.6833824999999999</v>
+        <v>0.6746276</v>
       </c>
       <c r="P77">
-        <v>2.0501475</v>
+        <v>2.0238828</v>
       </c>
       <c r="Q77">
-        <v>2.0901475</v>
+        <v>2.0638828</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.132220389953581</v>
+        <v>0.1355442511056418</v>
       </c>
       <c r="T77">
-        <v>1.639362863109664</v>
+        <v>1.702415280921574</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7892,7 +7892,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.040761935221038</v>
+        <v>2.013909804494445</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7900,22 +7900,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07573662026535403</v>
+        <v>0.08398114304231283</v>
       </c>
       <c r="C78">
-        <v>7.623458707498052</v>
+        <v>3.180657005222869</v>
       </c>
       <c r="D78">
-        <v>18.43545870749805</v>
+        <v>14.45465700522287</v>
       </c>
       <c r="E78">
-        <v>23.912</v>
+        <v>24.37400000000001</v>
       </c>
       <c r="F78">
-        <v>35.112</v>
+        <v>35.57400000000001</v>
       </c>
       <c r="G78">
         <v>24.3</v>
@@ -7936,45 +7936,45 @@
         <v>5.36</v>
       </c>
       <c r="M78">
-        <v>2.6614896</v>
+        <v>3.20166</v>
       </c>
       <c r="N78">
-        <v>2.6985104</v>
+        <v>2.15834</v>
       </c>
       <c r="O78">
-        <v>0.6746276</v>
+        <v>0.539585</v>
       </c>
       <c r="P78">
-        <v>2.0238828</v>
+        <v>1.618755</v>
       </c>
       <c r="Q78">
-        <v>2.0638828</v>
+        <v>1.658755</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1355442511056418</v>
+        <v>0.1391571436622296</v>
       </c>
       <c r="T78">
-        <v>1.702415280921574</v>
+        <v>1.77095051767365</v>
       </c>
       <c r="U78">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V78">
         <v>0.25</v>
       </c>
       <c r="W78">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y78">
-        <v>2.013909804494445</v>
+        <v>1.674131544261414</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7982,22 +7982,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08398114304231283</v>
+        <v>0.0841316658192716</v>
       </c>
       <c r="C79">
-        <v>3.180657005222869</v>
+        <v>2.661895707066122</v>
       </c>
       <c r="D79">
-        <v>14.45465700522287</v>
+        <v>14.39789570706612</v>
       </c>
       <c r="E79">
-        <v>24.37400000000001</v>
+        <v>24.836</v>
       </c>
       <c r="F79">
-        <v>35.57400000000001</v>
+        <v>36.036</v>
       </c>
       <c r="G79">
         <v>24.3</v>
@@ -8018,28 +8018,28 @@
         <v>5.36</v>
       </c>
       <c r="M79">
-        <v>3.20166</v>
+        <v>3.24324</v>
       </c>
       <c r="N79">
-        <v>2.15834</v>
+        <v>2.11676</v>
       </c>
       <c r="O79">
-        <v>0.539585</v>
+        <v>0.52919</v>
       </c>
       <c r="P79">
-        <v>1.618755</v>
+        <v>1.58757</v>
       </c>
       <c r="Q79">
-        <v>1.658755</v>
+        <v>1.62757</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1391571436622296</v>
+        <v>0.1430984809966891</v>
       </c>
       <c r="T79">
-        <v>1.77095051767365</v>
+        <v>1.845716230494097</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -8056,7 +8056,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.674131544261414</v>
+        <v>1.652668319334986</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8064,22 +8064,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.0841316658192716</v>
+        <v>0.08428218859623039</v>
       </c>
       <c r="C80">
-        <v>2.661895707066122</v>
+        <v>2.143578451648814</v>
       </c>
       <c r="D80">
-        <v>14.39789570706612</v>
+        <v>14.34157845164882</v>
       </c>
       <c r="E80">
-        <v>24.836</v>
+        <v>25.29800000000001</v>
       </c>
       <c r="F80">
-        <v>36.036</v>
+        <v>36.498</v>
       </c>
       <c r="G80">
         <v>24.3</v>
@@ -8100,28 +8100,28 @@
         <v>5.36</v>
       </c>
       <c r="M80">
-        <v>3.24324</v>
+        <v>3.28482</v>
       </c>
       <c r="N80">
-        <v>2.11676</v>
+        <v>2.07518</v>
       </c>
       <c r="O80">
-        <v>0.52919</v>
+        <v>0.518795</v>
       </c>
       <c r="P80">
-        <v>1.58757</v>
+        <v>1.556385</v>
       </c>
       <c r="Q80">
-        <v>1.62757</v>
+        <v>1.596385</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1430984809966891</v>
+        <v>0.1474151837915733</v>
       </c>
       <c r="T80">
-        <v>1.845716230494097</v>
+        <v>1.927602487392682</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -8138,7 +8138,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.652668319334986</v>
+        <v>1.631748467191505</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8146,22 +8146,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08428218859623039</v>
+        <v>0.08443271137318917</v>
       </c>
       <c r="C81">
-        <v>2.143578451648814</v>
+        <v>1.625700048663816</v>
       </c>
       <c r="D81">
-        <v>14.34157845164882</v>
+        <v>14.28570004866382</v>
       </c>
       <c r="E81">
-        <v>25.29800000000001</v>
+        <v>25.76</v>
       </c>
       <c r="F81">
-        <v>36.498</v>
+        <v>36.96</v>
       </c>
       <c r="G81">
         <v>24.3</v>
@@ -8182,28 +8182,28 @@
         <v>5.36</v>
       </c>
       <c r="M81">
-        <v>3.28482</v>
+        <v>3.3264</v>
       </c>
       <c r="N81">
-        <v>2.07518</v>
+        <v>2.0336</v>
       </c>
       <c r="O81">
-        <v>0.518795</v>
+        <v>0.5084000000000001</v>
       </c>
       <c r="P81">
-        <v>1.556385</v>
+        <v>1.5252</v>
       </c>
       <c r="Q81">
-        <v>1.596385</v>
+        <v>1.5652</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1474151837915733</v>
+        <v>0.1521635568659459</v>
       </c>
       <c r="T81">
-        <v>1.927602487392682</v>
+        <v>2.017677369981125</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.631748467191505</v>
+        <v>1.611351611351612</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8228,22 +8228,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08443271137318917</v>
+        <v>0.08458323415014796</v>
       </c>
       <c r="C82">
-        <v>1.625700048663816</v>
+        <v>1.108255388380961</v>
       </c>
       <c r="D82">
-        <v>14.28570004866382</v>
+        <v>14.23025538838097</v>
       </c>
       <c r="E82">
-        <v>25.76</v>
+        <v>26.222</v>
       </c>
       <c r="F82">
-        <v>36.96</v>
+        <v>37.422</v>
       </c>
       <c r="G82">
         <v>24.3</v>
@@ -8264,28 +8264,28 @@
         <v>5.36</v>
       </c>
       <c r="M82">
-        <v>3.3264</v>
+        <v>3.36798</v>
       </c>
       <c r="N82">
-        <v>2.0336</v>
+        <v>1.99202</v>
       </c>
       <c r="O82">
-        <v>0.5084000000000001</v>
+        <v>0.498005</v>
       </c>
       <c r="P82">
-        <v>1.5252</v>
+        <v>1.494015</v>
       </c>
       <c r="Q82">
-        <v>1.5652</v>
+        <v>1.534015</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1521635568659459</v>
+        <v>0.1574117586849893</v>
       </c>
       <c r="T82">
-        <v>2.017677369981125</v>
+        <v>2.117233819157825</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.611351611351612</v>
+        <v>1.591458381581838</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8310,22 +8310,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08458323415014796</v>
+        <v>0.08473375692710675</v>
       </c>
       <c r="C83">
-        <v>1.108255388380961</v>
+        <v>0.5912394400895593</v>
       </c>
       <c r="D83">
-        <v>14.23025538838097</v>
+        <v>14.17523944008956</v>
       </c>
       <c r="E83">
-        <v>26.222</v>
+        <v>26.68400000000001</v>
       </c>
       <c r="F83">
-        <v>37.422</v>
+        <v>37.88400000000001</v>
       </c>
       <c r="G83">
         <v>24.3</v>
@@ -8346,28 +8346,28 @@
         <v>5.36</v>
       </c>
       <c r="M83">
-        <v>3.36798</v>
+        <v>3.40956</v>
       </c>
       <c r="N83">
-        <v>1.99202</v>
+        <v>1.95044</v>
       </c>
       <c r="O83">
-        <v>0.498005</v>
+        <v>0.48761</v>
       </c>
       <c r="P83">
-        <v>1.494015</v>
+        <v>1.46283</v>
       </c>
       <c r="Q83">
-        <v>1.534015</v>
+        <v>1.50283</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1574117586849893</v>
+        <v>0.1632430940394819</v>
       </c>
       <c r="T83">
-        <v>2.117233819157825</v>
+        <v>2.227852096020825</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8384,7 +8384,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.591458381581838</v>
+        <v>1.572050352538157</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8392,22 +8392,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08473375692710675</v>
+        <v>0.08488427970406552</v>
       </c>
       <c r="C84">
-        <v>0.5912394400895593</v>
+        <v>0.07464725057670307</v>
       </c>
       <c r="D84">
-        <v>14.17523944008956</v>
+        <v>14.12064725057671</v>
       </c>
       <c r="E84">
-        <v>26.68400000000001</v>
+        <v>27.146</v>
       </c>
       <c r="F84">
-        <v>37.88400000000001</v>
+        <v>38.346</v>
       </c>
       <c r="G84">
         <v>24.3</v>
@@ -8428,28 +8428,28 @@
         <v>5.36</v>
       </c>
       <c r="M84">
-        <v>3.40956</v>
+        <v>3.45114</v>
       </c>
       <c r="N84">
-        <v>1.95044</v>
+        <v>1.90886</v>
       </c>
       <c r="O84">
-        <v>0.48761</v>
+        <v>0.4772150000000001</v>
       </c>
       <c r="P84">
-        <v>1.46283</v>
+        <v>1.431645</v>
       </c>
       <c r="Q84">
-        <v>1.50283</v>
+        <v>1.471645</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1632430940394819</v>
+        <v>0.1697604688474443</v>
       </c>
       <c r="T84">
-        <v>2.227852096020825</v>
+        <v>2.351484287808885</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8466,7 +8466,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.572050352538157</v>
+        <v>1.553109986844927</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8474,22 +8474,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08488427970406552</v>
+        <v>0.08503480248102431</v>
       </c>
       <c r="C85">
-        <v>0.07464725057670307</v>
+        <v>-0.4415260573592903</v>
       </c>
       <c r="D85">
-        <v>14.12064725057671</v>
+        <v>14.06647394264072</v>
       </c>
       <c r="E85">
-        <v>27.146</v>
+        <v>27.60800000000001</v>
       </c>
       <c r="F85">
-        <v>38.346</v>
+        <v>38.80800000000001</v>
       </c>
       <c r="G85">
         <v>24.3</v>
@@ -8510,28 +8510,28 @@
         <v>5.36</v>
       </c>
       <c r="M85">
-        <v>3.45114</v>
+        <v>3.492720000000001</v>
       </c>
       <c r="N85">
-        <v>1.90886</v>
+        <v>1.86728</v>
       </c>
       <c r="O85">
-        <v>0.4772150000000001</v>
+        <v>0.4668199999999999</v>
       </c>
       <c r="P85">
-        <v>1.431645</v>
+        <v>1.40046</v>
       </c>
       <c r="Q85">
-        <v>1.471645</v>
+        <v>1.44046</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1697604688474443</v>
+        <v>0.177092515506402</v>
       </c>
       <c r="T85">
-        <v>2.351484287808885</v>
+        <v>2.490570503570452</v>
       </c>
       <c r="U85">
         <v>0.09</v>
@@ -8548,7 +8548,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.553109986844927</v>
+        <v>1.53462058223963</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8556,22 +8556,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08503480248102431</v>
+        <v>0.0851853252579831</v>
       </c>
       <c r="C86">
-        <v>-0.4415260573592832</v>
+        <v>-0.9572852863613548</v>
       </c>
       <c r="D86">
-        <v>14.06647394264072</v>
+        <v>14.01271471363865</v>
       </c>
       <c r="E86">
-        <v>27.608</v>
+        <v>28.07</v>
       </c>
       <c r="F86">
-        <v>38.808</v>
+        <v>39.27</v>
       </c>
       <c r="G86">
         <v>24.3</v>
@@ -8592,28 +8592,28 @@
         <v>5.36</v>
       </c>
       <c r="M86">
-        <v>3.49272</v>
+        <v>3.5343</v>
       </c>
       <c r="N86">
-        <v>1.86728</v>
+        <v>1.8257</v>
       </c>
       <c r="O86">
-        <v>0.4668200000000001</v>
+        <v>0.4564250000000001</v>
       </c>
       <c r="P86">
-        <v>1.40046</v>
+        <v>1.369275</v>
       </c>
       <c r="Q86">
-        <v>1.44046</v>
+        <v>1.409275</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1770925155064019</v>
+        <v>0.185402168386554</v>
       </c>
       <c r="T86">
-        <v>2.49057050357045</v>
+        <v>2.648201548100226</v>
       </c>
       <c r="U86">
         <v>0.09</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>1.53462058223963</v>
+        <v>1.516566222448576</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8638,22 +8638,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.0851853252579831</v>
+        <v>0.1249928074917717</v>
       </c>
       <c r="C87">
-        <v>-0.9572852863613548</v>
+        <v>-8.462991775341123</v>
       </c>
       <c r="D87">
-        <v>14.01271471363865</v>
+        <v>6.969008224658875</v>
       </c>
       <c r="E87">
-        <v>28.07</v>
+        <v>28.532</v>
       </c>
       <c r="F87">
-        <v>39.27</v>
+        <v>39.732</v>
       </c>
       <c r="G87">
         <v>24.3</v>
@@ -8674,45 +8674,45 @@
         <v>5.36</v>
       </c>
       <c r="M87">
-        <v>3.5343</v>
+        <v>5.8326576</v>
       </c>
       <c r="N87">
-        <v>1.8257</v>
+        <v>-0.4726575999999998</v>
       </c>
       <c r="O87">
-        <v>0.4564250000000001</v>
+        <v>-0.1181643999999999</v>
       </c>
       <c r="P87">
-        <v>1.369275</v>
+        <v>-0.3544931999999998</v>
       </c>
       <c r="Q87">
-        <v>1.409275</v>
+        <v>-0.3144931999999998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.185402168386554</v>
+        <v>0.1982081178292903</v>
       </c>
       <c r="T87">
-        <v>2.648201548100226</v>
+        <v>2.891125676937856</v>
       </c>
       <c r="U87">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.25</v>
+        <v>0.2297408989000143</v>
       </c>
       <c r="W87">
-        <v>0.0675</v>
+        <v>0.1130740360414779</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y87">
-        <v>1.516566222448576</v>
+        <v>0.9189635956000572</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8720,22 +8720,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1249928074917717</v>
+        <v>0.1260028074917716</v>
       </c>
       <c r="C88">
-        <v>-8.462991775341123</v>
+        <v>-9.012753021200599</v>
       </c>
       <c r="D88">
-        <v>6.969008224658875</v>
+        <v>6.881246978799402</v>
       </c>
       <c r="E88">
-        <v>28.532</v>
+        <v>28.994</v>
       </c>
       <c r="F88">
-        <v>39.732</v>
+        <v>40.194</v>
       </c>
       <c r="G88">
         <v>24.3</v>
@@ -8756,37 +8756,37 @@
         <v>5.36</v>
       </c>
       <c r="M88">
-        <v>5.8326576</v>
+        <v>5.900479200000001</v>
       </c>
       <c r="N88">
-        <v>-0.4726575999999998</v>
+        <v>-0.5404792000000009</v>
       </c>
       <c r="O88">
-        <v>-0.1181643999999999</v>
+        <v>-0.1351198000000002</v>
       </c>
       <c r="P88">
-        <v>-0.3544931999999998</v>
+        <v>-0.4053594000000007</v>
       </c>
       <c r="Q88">
-        <v>-0.3144931999999998</v>
+        <v>-0.3653594000000007</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.1982081178292903</v>
+        <v>0.2099318192007742</v>
       </c>
       <c r="T88">
-        <v>2.891125676937856</v>
+        <v>3.11351995977923</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2297408989000143</v>
+        <v>0.2271001989126578</v>
       </c>
       <c r="W88">
-        <v>0.1130740360414779</v>
+        <v>0.1134616907996218</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8794,7 +8794,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9189635956000572</v>
+        <v>0.908400795650631</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8802,22 +8802,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1260028074917716</v>
+        <v>0.1270128074917717</v>
       </c>
       <c r="C89">
-        <v>-9.012753021200599</v>
+        <v>-9.560331388249317</v>
       </c>
       <c r="D89">
-        <v>6.881246978799402</v>
+        <v>6.795668611750687</v>
       </c>
       <c r="E89">
-        <v>28.994</v>
+        <v>29.45600000000001</v>
       </c>
       <c r="F89">
-        <v>40.194</v>
+        <v>40.65600000000001</v>
       </c>
       <c r="G89">
         <v>24.3</v>
@@ -8838,37 +8838,37 @@
         <v>5.36</v>
       </c>
       <c r="M89">
-        <v>5.900479200000001</v>
+        <v>5.968300800000002</v>
       </c>
       <c r="N89">
-        <v>-0.5404792000000009</v>
+        <v>-0.6083008000000012</v>
       </c>
       <c r="O89">
-        <v>-0.1351198000000002</v>
+        <v>-0.1520752000000003</v>
       </c>
       <c r="P89">
-        <v>-0.4053594000000007</v>
+        <v>-0.4562256000000009</v>
       </c>
       <c r="Q89">
-        <v>-0.3653594000000007</v>
+        <v>-0.4162256000000009</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2099318192007742</v>
+        <v>0.2236094708008388</v>
       </c>
       <c r="T89">
-        <v>3.11351995977923</v>
+        <v>3.372979956427499</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2271001989126578</v>
+        <v>0.2245195148341048</v>
       </c>
       <c r="W89">
-        <v>0.1134616907996218</v>
+        <v>0.1138405352223534</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.908400795650631</v>
+        <v>0.8980780593364194</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8884,22 +8884,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1270128074917717</v>
+        <v>0.1280228074917717</v>
       </c>
       <c r="C90">
-        <v>-9.560331388249317</v>
+        <v>-10.10580731794869</v>
       </c>
       <c r="D90">
-        <v>6.795668611750687</v>
+        <v>6.712192682051314</v>
       </c>
       <c r="E90">
-        <v>29.45600000000001</v>
+        <v>29.918</v>
       </c>
       <c r="F90">
-        <v>40.65600000000001</v>
+        <v>41.118</v>
       </c>
       <c r="G90">
         <v>24.3</v>
@@ -8920,37 +8920,37 @@
         <v>5.36</v>
       </c>
       <c r="M90">
-        <v>5.968300800000002</v>
+        <v>6.036122400000001</v>
       </c>
       <c r="N90">
-        <v>-0.6083008000000012</v>
+        <v>-0.6761224000000006</v>
       </c>
       <c r="O90">
-        <v>-0.1520752000000003</v>
+        <v>-0.1690306000000001</v>
       </c>
       <c r="P90">
-        <v>-0.4562256000000009</v>
+        <v>-0.5070918000000004</v>
       </c>
       <c r="Q90">
-        <v>-0.4162256000000009</v>
+        <v>-0.4670918000000004</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2236094708008388</v>
+        <v>0.2397739681463696</v>
       </c>
       <c r="T90">
-        <v>3.372979956427499</v>
+        <v>3.679614497920908</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.2245195148341048</v>
+        <v>0.2219968236561936</v>
       </c>
       <c r="W90">
-        <v>0.1138405352223534</v>
+        <v>0.1142108662872708</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8980780593364194</v>
+        <v>0.8879872946247742</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8966,22 +8966,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1280228074917717</v>
+        <v>0.1290328074917717</v>
       </c>
       <c r="C91">
-        <v>-10.10580731794869</v>
+        <v>-10.64925734724804</v>
       </c>
       <c r="D91">
-        <v>6.712192682051314</v>
+        <v>6.630742652751967</v>
       </c>
       <c r="E91">
-        <v>29.918</v>
+        <v>30.38000000000001</v>
       </c>
       <c r="F91">
-        <v>41.118</v>
+        <v>41.58000000000001</v>
       </c>
       <c r="G91">
         <v>24.3</v>
@@ -9002,37 +9002,37 @@
         <v>5.36</v>
       </c>
       <c r="M91">
-        <v>6.036122400000001</v>
+        <v>6.103944000000001</v>
       </c>
       <c r="N91">
-        <v>-0.6761224000000006</v>
+        <v>-0.7439440000000008</v>
       </c>
       <c r="O91">
-        <v>-0.1690306000000001</v>
+        <v>-0.1859860000000002</v>
       </c>
       <c r="P91">
-        <v>-0.5070918000000004</v>
+        <v>-0.5579580000000006</v>
       </c>
       <c r="Q91">
-        <v>-0.4670918000000004</v>
+        <v>-0.5179580000000006</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2397739681463696</v>
+        <v>0.2591713649610066</v>
       </c>
       <c r="T91">
-        <v>3.679614497920908</v>
+        <v>4.047575947713</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2219968236561936</v>
+        <v>0.2195301922822359</v>
       </c>
       <c r="W91">
-        <v>0.1142108662872708</v>
+        <v>0.1145729677729678</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9040,7 +9040,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8879872946247742</v>
+        <v>0.8781207691289434</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9048,22 +9048,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1290328074917717</v>
+        <v>0.1300428074917717</v>
       </c>
       <c r="C92">
-        <v>-10.64925734724804</v>
+        <v>-11.19075434264356</v>
       </c>
       <c r="D92">
-        <v>6.630742652751967</v>
+        <v>6.55124565735644</v>
       </c>
       <c r="E92">
-        <v>30.38000000000001</v>
+        <v>30.842</v>
       </c>
       <c r="F92">
-        <v>41.58000000000001</v>
+        <v>42.042</v>
       </c>
       <c r="G92">
         <v>24.3</v>
@@ -9084,37 +9084,37 @@
         <v>5.36</v>
       </c>
       <c r="M92">
-        <v>6.103944000000001</v>
+        <v>6.171765600000001</v>
       </c>
       <c r="N92">
-        <v>-0.7439440000000008</v>
+        <v>-0.8117656000000002</v>
       </c>
       <c r="O92">
-        <v>-0.1859860000000002</v>
+        <v>-0.2029414</v>
       </c>
       <c r="P92">
-        <v>-0.5579580000000006</v>
+        <v>-0.6088242000000001</v>
       </c>
       <c r="Q92">
-        <v>-0.5179580000000006</v>
+        <v>-0.5688242000000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2591713649610066</v>
+        <v>0.2828792944011184</v>
       </c>
       <c r="T92">
-        <v>4.047575947713</v>
+        <v>4.49730660857</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2195301922822359</v>
+        <v>0.2171177725868267</v>
       </c>
       <c r="W92">
-        <v>0.1145729677729678</v>
+        <v>0.1149271109842538</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9122,7 +9122,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8781207691289434</v>
+        <v>0.8684710903473067</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9130,22 +9130,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1300428074917717</v>
+        <v>0.1310528074917717</v>
       </c>
       <c r="C93">
-        <v>-11.19075434264356</v>
+        <v>-11.73036771759979</v>
       </c>
       <c r="D93">
-        <v>6.55124565735644</v>
+        <v>6.473632282400211</v>
       </c>
       <c r="E93">
-        <v>30.842</v>
+        <v>31.30400000000001</v>
       </c>
       <c r="F93">
-        <v>42.042</v>
+        <v>42.504</v>
       </c>
       <c r="G93">
         <v>24.3</v>
@@ -9166,37 +9166,37 @@
         <v>5.36</v>
       </c>
       <c r="M93">
-        <v>6.171765600000001</v>
+        <v>6.239587200000002</v>
       </c>
       <c r="N93">
-        <v>-0.8117656000000002</v>
+        <v>-0.8795872000000013</v>
       </c>
       <c r="O93">
-        <v>-0.2029414</v>
+        <v>-0.2198968000000003</v>
       </c>
       <c r="P93">
-        <v>-0.6088242000000001</v>
+        <v>-0.659690400000001</v>
       </c>
       <c r="Q93">
-        <v>-0.5688242000000001</v>
+        <v>-0.619690400000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2828792944011184</v>
+        <v>0.3125142062012583</v>
       </c>
       <c r="T93">
-        <v>4.49730660857</v>
+        <v>5.059469934641251</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2171177725868267</v>
+        <v>0.2147577967978394</v>
       </c>
       <c r="W93">
-        <v>0.1149271109842538</v>
+        <v>0.1152735554300772</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9204,7 +9204,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8684710903473067</v>
+        <v>0.8590311871913576</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9212,22 +9212,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1310528074917717</v>
+        <v>0.1320628074917717</v>
       </c>
       <c r="C94">
-        <v>-11.73036771759979</v>
+        <v>-12.26816363469707</v>
       </c>
       <c r="D94">
-        <v>6.473632282400211</v>
+        <v>6.39783636530294</v>
       </c>
       <c r="E94">
-        <v>31.30400000000001</v>
+        <v>31.76600000000001</v>
       </c>
       <c r="F94">
-        <v>42.504</v>
+        <v>42.96600000000001</v>
       </c>
       <c r="G94">
         <v>24.3</v>
@@ -9248,37 +9248,37 @@
         <v>5.36</v>
       </c>
       <c r="M94">
-        <v>6.239587200000002</v>
+        <v>6.307408800000002</v>
       </c>
       <c r="N94">
-        <v>-0.8795872000000013</v>
+        <v>-0.9474088000000016</v>
       </c>
       <c r="O94">
-        <v>-0.2198968000000003</v>
+        <v>-0.2368522000000004</v>
       </c>
       <c r="P94">
-        <v>-0.659690400000001</v>
+        <v>-0.7105566000000012</v>
       </c>
       <c r="Q94">
-        <v>-0.619690400000001</v>
+        <v>-0.6705566000000012</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3125142062012583</v>
+        <v>0.3506162356585809</v>
       </c>
       <c r="T94">
-        <v>5.059469934641251</v>
+        <v>5.782251353875716</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2147577967978394</v>
+        <v>0.2124485731763573</v>
       </c>
       <c r="W94">
-        <v>0.1152735554300772</v>
+        <v>0.1156125494577108</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9286,7 +9286,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8590311871913576</v>
+        <v>0.8497942927054289</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9294,22 +9294,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1320628074917717</v>
+        <v>0.1330728074917717</v>
       </c>
       <c r="C95">
-        <v>-12.26816363469707</v>
+        <v>-12.80420519374242</v>
       </c>
       <c r="D95">
-        <v>6.39783636530294</v>
+        <v>6.323794806257584</v>
       </c>
       <c r="E95">
-        <v>31.76600000000001</v>
+        <v>32.22800000000001</v>
       </c>
       <c r="F95">
-        <v>42.96600000000001</v>
+        <v>43.428</v>
       </c>
       <c r="G95">
         <v>24.3</v>
@@ -9330,37 +9330,37 @@
         <v>5.36</v>
       </c>
       <c r="M95">
-        <v>6.307408800000002</v>
+        <v>6.375230400000001</v>
       </c>
       <c r="N95">
-        <v>-0.9474088000000016</v>
+        <v>-1.015230400000001</v>
       </c>
       <c r="O95">
-        <v>-0.2368522000000004</v>
+        <v>-0.2538076000000002</v>
       </c>
       <c r="P95">
-        <v>-0.7105566000000012</v>
+        <v>-0.7614228000000007</v>
       </c>
       <c r="Q95">
-        <v>-0.6705566000000012</v>
+        <v>-0.7214228000000007</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3506162356585809</v>
+        <v>0.4014189416016778</v>
       </c>
       <c r="T95">
-        <v>5.782251353875716</v>
+        <v>6.745959912855004</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.2124485731763573</v>
+        <v>0.2101884819723535</v>
       </c>
       <c r="W95">
-        <v>0.1156125494577108</v>
+        <v>0.1159443308464585</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9368,7 +9368,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8497942927054289</v>
+        <v>0.8407539278894138</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9376,22 +9376,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1330728074917717</v>
+        <v>0.1340828074917716</v>
       </c>
       <c r="C96">
-        <v>-12.80420519374242</v>
+        <v>-13.33855260696799</v>
       </c>
       <c r="D96">
-        <v>6.323794806257584</v>
+        <v>6.251447393032022</v>
       </c>
       <c r="E96">
-        <v>32.22800000000001</v>
+        <v>32.69000000000001</v>
       </c>
       <c r="F96">
-        <v>43.428</v>
+        <v>43.89000000000001</v>
       </c>
       <c r="G96">
         <v>24.3</v>
@@ -9412,37 +9412,37 @@
         <v>5.36</v>
       </c>
       <c r="M96">
-        <v>6.375230400000001</v>
+        <v>6.443052000000002</v>
       </c>
       <c r="N96">
-        <v>-1.015230400000001</v>
+        <v>-1.083052000000001</v>
       </c>
       <c r="O96">
-        <v>-0.2538076000000002</v>
+        <v>-0.2707630000000003</v>
       </c>
       <c r="P96">
-        <v>-0.7614228000000007</v>
+        <v>-0.8122890000000009</v>
       </c>
       <c r="Q96">
-        <v>-0.7214228000000007</v>
+        <v>-0.7722890000000009</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4014189416016778</v>
+        <v>0.4725427299220136</v>
       </c>
       <c r="T96">
-        <v>6.745959912855004</v>
+        <v>8.095151895426008</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.2101884819723535</v>
+        <v>0.2079759716358024</v>
       </c>
       <c r="W96">
-        <v>0.1159443308464585</v>
+        <v>0.1162691273638642</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8407539278894138</v>
+        <v>0.8319038865432095</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9458,22 +9458,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1340828074917716</v>
+        <v>0.1350928074917717</v>
       </c>
       <c r="C97">
-        <v>-13.33855260696799</v>
+        <v>-13.87126336233923</v>
       </c>
       <c r="D97">
-        <v>6.251447393032022</v>
+        <v>6.180736637660775</v>
       </c>
       <c r="E97">
-        <v>32.69000000000001</v>
+        <v>33.152</v>
       </c>
       <c r="F97">
-        <v>43.89000000000001</v>
+        <v>44.352</v>
       </c>
       <c r="G97">
         <v>24.3</v>
@@ -9494,37 +9494,37 @@
         <v>5.36</v>
       </c>
       <c r="M97">
-        <v>6.443052000000002</v>
+        <v>6.510873600000001</v>
       </c>
       <c r="N97">
-        <v>-1.083052000000001</v>
+        <v>-1.150873600000001</v>
       </c>
       <c r="O97">
-        <v>-0.2707630000000003</v>
+        <v>-0.2877184000000002</v>
       </c>
       <c r="P97">
-        <v>-0.8122890000000009</v>
+        <v>-0.8631552000000005</v>
       </c>
       <c r="Q97">
-        <v>-0.7722890000000009</v>
+        <v>-0.8231552000000004</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4725427299220136</v>
+        <v>0.5792284124025172</v>
       </c>
       <c r="T97">
-        <v>8.095151895426008</v>
+        <v>10.11893986928252</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2079759716358024</v>
+        <v>0.2058095552645961</v>
       </c>
       <c r="W97">
-        <v>0.1162691273638642</v>
+        <v>0.1165871572871573</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9532,7 +9532,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8319038865432095</v>
+        <v>0.8232382210583845</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9540,22 +9540,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1350928074917717</v>
+        <v>0.1361028074917716</v>
       </c>
       <c r="C98">
-        <v>-13.87126336233923</v>
+        <v>-14.40239237590401</v>
       </c>
       <c r="D98">
-        <v>6.180736637660775</v>
+        <v>6.111607624095985</v>
       </c>
       <c r="E98">
-        <v>33.152</v>
+        <v>33.614</v>
       </c>
       <c r="F98">
-        <v>44.352</v>
+        <v>44.814</v>
       </c>
       <c r="G98">
         <v>24.3</v>
@@ -9576,37 +9576,37 @@
         <v>5.36</v>
       </c>
       <c r="M98">
-        <v>6.510873600000001</v>
+        <v>6.5786952</v>
       </c>
       <c r="N98">
-        <v>-1.150873600000001</v>
+        <v>-1.2186952</v>
       </c>
       <c r="O98">
-        <v>-0.2877184000000002</v>
+        <v>-0.3046738</v>
       </c>
       <c r="P98">
-        <v>-0.8631552000000005</v>
+        <v>-0.9140214</v>
       </c>
       <c r="Q98">
-        <v>-0.8231552000000004</v>
+        <v>-0.8740213999999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5792284124025157</v>
+        <v>0.7570378832033543</v>
       </c>
       <c r="T98">
-        <v>10.11893986928249</v>
+        <v>13.49191982570998</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.2058095552645961</v>
+        <v>0.2036878072721776</v>
       </c>
       <c r="W98">
-        <v>0.1165871572871573</v>
+        <v>0.1168986298924443</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.8232382210583845</v>
+        <v>0.8147512290887104</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9622,22 +9622,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1361028074917716</v>
+        <v>0.1371128074917717</v>
       </c>
       <c r="C99">
-        <v>-14.40239237590401</v>
+        <v>-14.93199213403097</v>
       </c>
       <c r="D99">
-        <v>6.111607624095985</v>
+        <v>6.04400786596903</v>
       </c>
       <c r="E99">
-        <v>33.614</v>
+        <v>34.07600000000001</v>
       </c>
       <c r="F99">
-        <v>44.814</v>
+        <v>45.276</v>
       </c>
       <c r="G99">
         <v>24.3</v>
@@ -9658,37 +9658,37 @@
         <v>5.36</v>
       </c>
       <c r="M99">
-        <v>6.5786952</v>
+        <v>6.646516800000001</v>
       </c>
       <c r="N99">
-        <v>-1.2186952</v>
+        <v>-1.286516800000001</v>
       </c>
       <c r="O99">
-        <v>-0.3046738</v>
+        <v>-0.3216292000000003</v>
       </c>
       <c r="P99">
-        <v>-0.9140214</v>
+        <v>-0.9648876000000008</v>
       </c>
       <c r="Q99">
-        <v>-0.8740213999999999</v>
+        <v>-0.9248876000000008</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7570378832033543</v>
+        <v>1.112656824805031</v>
       </c>
       <c r="T99">
-        <v>13.49191982570998</v>
+        <v>20.23787973856497</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.2036878072721776</v>
+        <v>0.2016093602591962</v>
       </c>
       <c r="W99">
-        <v>0.1168986298924443</v>
+        <v>0.11720374591395</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9696,7 +9696,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8147512290887104</v>
+        <v>0.8064374410367847</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9704,22 +9704,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1371128074917717</v>
+        <v>0.1929956692791264</v>
       </c>
       <c r="C100">
-        <v>-14.93199213403097</v>
+        <v>-17.68860078569685</v>
       </c>
       <c r="D100">
-        <v>6.04400786596903</v>
+        <v>3.749399214303155</v>
       </c>
       <c r="E100">
-        <v>34.07600000000001</v>
+        <v>34.538</v>
       </c>
       <c r="F100">
-        <v>45.276</v>
+        <v>45.738</v>
       </c>
       <c r="G100">
         <v>24.3</v>
@@ -9740,129 +9740,47 @@
         <v>5.36</v>
       </c>
       <c r="M100">
-        <v>6.646516800000001</v>
+        <v>9.1841904</v>
       </c>
       <c r="N100">
-        <v>-1.286516800000001</v>
+        <v>-3.8241904</v>
       </c>
       <c r="O100">
-        <v>-0.3216292000000003</v>
+        <v>-0.9560476</v>
       </c>
       <c r="P100">
-        <v>-0.9648876000000008</v>
+        <v>-2.8681428</v>
       </c>
       <c r="Q100">
-        <v>-0.9248876000000008</v>
+        <v>-2.8281428</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.112656824805031</v>
+        <v>2.320799828345538</v>
       </c>
       <c r="T100">
-        <v>20.23787973856497</v>
+        <v>43.15590607926889</v>
       </c>
       <c r="U100">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.2016093602591962</v>
+        <v>0.1459028985287587</v>
       </c>
       <c r="W100">
-        <v>0.11720374591395</v>
+        <v>0.1715026979754253</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.8064374410367847</v>
+        <v>0.5836115941150349</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1929956692791264</v>
-      </c>
-      <c r="C101">
-        <v>-17.68860078569685</v>
-      </c>
-      <c r="D101">
-        <v>3.749399214303155</v>
-      </c>
-      <c r="E101">
-        <v>34.538</v>
-      </c>
-      <c r="F101">
-        <v>45.738</v>
-      </c>
-      <c r="G101">
-        <v>24.3</v>
-      </c>
-      <c r="H101">
-        <v>35</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>5.4</v>
-      </c>
-      <c r="K101">
-        <v>0.04000000000000004</v>
-      </c>
-      <c r="L101">
-        <v>5.36</v>
-      </c>
-      <c r="M101">
-        <v>9.1841904</v>
-      </c>
-      <c r="N101">
-        <v>-3.8241904</v>
-      </c>
-      <c r="O101">
-        <v>-0.9560476</v>
-      </c>
-      <c r="P101">
-        <v>-2.8681428</v>
-      </c>
-      <c r="Q101">
-        <v>-2.8281428</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.320799828345538</v>
-      </c>
-      <c r="T101">
-        <v>43.15590607926889</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1459028985287587</v>
-      </c>
-      <c r="W101">
-        <v>0.1715026979754253</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5836115941150349</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
